--- a/research/traditional_assets/database/data/argentina/argentina_diversified.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_diversified.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1940093548786357</v>
+        <v>0.1933595721365605</v>
       </c>
       <c r="C2">
-        <v>21.79118470215076</v>
+        <v>21.68058907483802</v>
       </c>
       <c r="D2">
-        <v>21.52918470215076</v>
+        <v>21.62398907483803</v>
       </c>
       <c r="E2">
-        <v>-12.1</v>
+        <v>-11.8946</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2054</v>
       </c>
       <c r="G2">
         <v>0.262</v>
@@ -1439,28 +1439,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01033162</v>
       </c>
       <c r="N2">
-        <v>8.359999999999999</v>
+        <v>8.349668379999999</v>
       </c>
       <c r="O2">
-        <v>2.926</v>
+        <v>2.922383932999999</v>
       </c>
       <c r="P2">
-        <v>5.433999999999999</v>
+        <v>5.427284447</v>
       </c>
       <c r="Q2">
-        <v>7.074</v>
+        <v>7.067284447</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1940093548786357</v>
+        <v>0.1949824466025864</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7329888836530167</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>809.1664230778908</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1933595721365605</v>
+        <v>0.1927097893944853</v>
       </c>
       <c r="C3">
-        <v>21.68058907483802</v>
+        <v>21.57083208796579</v>
       </c>
       <c r="D3">
-        <v>21.62398907483803</v>
+        <v>21.71963208796578</v>
       </c>
       <c r="E3">
-        <v>-11.8946</v>
+        <v>-11.6892</v>
       </c>
       <c r="F3">
-        <v>0.2054</v>
+        <v>0.4108</v>
       </c>
       <c r="G3">
         <v>0.262</v>
@@ -1521,28 +1521,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M3">
-        <v>0.01033162</v>
+        <v>0.02066324</v>
       </c>
       <c r="N3">
-        <v>8.349668379999999</v>
+        <v>8.33933676</v>
       </c>
       <c r="O3">
-        <v>2.922383932999999</v>
+        <v>2.918767866</v>
       </c>
       <c r="P3">
-        <v>5.427284447</v>
+        <v>5.420568894000001</v>
       </c>
       <c r="Q3">
-        <v>7.067284447</v>
+        <v>7.060568894000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1949824466025864</v>
+        <v>0.1959753973413115</v>
       </c>
       <c r="T3">
-        <v>0.7329888836530167</v>
+        <v>0.7378676201939146</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>809.1664230778908</v>
+        <v>404.5832115389455</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1927097893944853</v>
+        <v>0.1920600066524101</v>
       </c>
       <c r="C4">
-        <v>21.57083208796579</v>
+        <v>21.46192491890434</v>
       </c>
       <c r="D4">
-        <v>21.71963208796578</v>
+        <v>21.81612491890434</v>
       </c>
       <c r="E4">
-        <v>-11.6892</v>
+        <v>-11.4838</v>
       </c>
       <c r="F4">
-        <v>0.4108</v>
+        <v>0.6162</v>
       </c>
       <c r="G4">
         <v>0.262</v>
@@ -1603,28 +1603,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M4">
-        <v>0.02066324</v>
+        <v>0.03099486</v>
       </c>
       <c r="N4">
-        <v>8.33933676</v>
+        <v>8.32900514</v>
       </c>
       <c r="O4">
-        <v>2.918767866</v>
+        <v>2.915151799</v>
       </c>
       <c r="P4">
-        <v>5.420568894000001</v>
+        <v>5.413853340999999</v>
       </c>
       <c r="Q4">
-        <v>7.060568894000001</v>
+        <v>7.053853341</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1959753973413115</v>
+        <v>0.1969888212911444</v>
       </c>
       <c r="T4">
-        <v>0.7378676201939146</v>
+        <v>0.7428469492408102</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>404.5832115389455</v>
+        <v>269.7221410259637</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1920600066524101</v>
+        <v>0.1914102239103349</v>
       </c>
       <c r="C5">
-        <v>21.46192491890434</v>
+        <v>21.35387894453918</v>
       </c>
       <c r="D5">
-        <v>21.81612491890434</v>
+        <v>21.91347894453918</v>
       </c>
       <c r="E5">
-        <v>-11.4838</v>
+        <v>-11.2784</v>
       </c>
       <c r="F5">
-        <v>0.6162</v>
+        <v>0.8216</v>
       </c>
       <c r="G5">
         <v>0.262</v>
@@ -1685,28 +1685,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M5">
-        <v>0.03099486</v>
+        <v>0.04132648</v>
       </c>
       <c r="N5">
-        <v>8.32900514</v>
+        <v>8.318673519999999</v>
       </c>
       <c r="O5">
-        <v>2.915151799</v>
+        <v>2.911535731999999</v>
       </c>
       <c r="P5">
-        <v>5.413853340999999</v>
+        <v>5.407137788</v>
       </c>
       <c r="Q5">
-        <v>7.053853341</v>
+        <v>7.047137788000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1969888212911444</v>
+        <v>0.1980233582399321</v>
       </c>
       <c r="T5">
-        <v>0.7428469492408102</v>
+        <v>0.7479300143095163</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>269.7221410259637</v>
+        <v>202.2916057694727</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1914102239103349</v>
+        <v>0.1907604411682596</v>
       </c>
       <c r="C6">
-        <v>21.35387894453918</v>
+        <v>21.24670574574257</v>
       </c>
       <c r="D6">
-        <v>21.91347894453918</v>
+        <v>22.01170574574257</v>
       </c>
       <c r="E6">
-        <v>-11.2784</v>
+        <v>-11.073</v>
       </c>
       <c r="F6">
-        <v>0.8216</v>
+        <v>1.027</v>
       </c>
       <c r="G6">
         <v>0.262</v>
@@ -1767,28 +1767,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M6">
-        <v>0.04132648</v>
+        <v>0.05165809999999999</v>
       </c>
       <c r="N6">
-        <v>8.318673519999999</v>
+        <v>8.3083419</v>
       </c>
       <c r="O6">
-        <v>2.911535731999999</v>
+        <v>2.907919665</v>
       </c>
       <c r="P6">
-        <v>5.407137788</v>
+        <v>5.400422235000001</v>
       </c>
       <c r="Q6">
-        <v>7.047137788000001</v>
+        <v>7.040422235000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1980233582399321</v>
+        <v>0.1990796749139575</v>
       </c>
       <c r="T6">
-        <v>0.7479300143095163</v>
+        <v>0.7531200912744057</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>202.2916057694727</v>
+        <v>161.8332846155782</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1907604411682596</v>
+        <v>0.1901106584261844</v>
       </c>
       <c r="C7">
-        <v>21.24670574574257</v>
+        <v>21.140417111966</v>
       </c>
       <c r="D7">
-        <v>22.01170574574257</v>
+        <v>22.110817111966</v>
       </c>
       <c r="E7">
-        <v>-11.073</v>
+        <v>-10.8676</v>
       </c>
       <c r="F7">
-        <v>1.027</v>
+        <v>1.2324</v>
       </c>
       <c r="G7">
         <v>0.262</v>
@@ -1849,28 +1849,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M7">
-        <v>0.05165809999999999</v>
+        <v>0.06198971999999999</v>
       </c>
       <c r="N7">
-        <v>8.3083419</v>
+        <v>8.29801028</v>
       </c>
       <c r="O7">
-        <v>2.907919665</v>
+        <v>2.904303598</v>
       </c>
       <c r="P7">
-        <v>5.400422235000001</v>
+        <v>5.393706681999999</v>
       </c>
       <c r="Q7">
-        <v>7.040422235000001</v>
+        <v>7.033706682</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1990796749139575</v>
+        <v>0.2001584664108345</v>
       </c>
       <c r="T7">
-        <v>0.7531200912744057</v>
+        <v>0.7584205954087608</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>161.8332846155782</v>
+        <v>134.8610705129819</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1901106584261844</v>
+        <v>0.1894608756841092</v>
       </c>
       <c r="C8">
-        <v>21.140417111966</v>
+        <v>21.03502504595722</v>
       </c>
       <c r="D8">
-        <v>22.110817111966</v>
+        <v>22.21082504595722</v>
       </c>
       <c r="E8">
-        <v>-10.8676</v>
+        <v>-10.6622</v>
       </c>
       <c r="F8">
-        <v>1.2324</v>
+        <v>1.4378</v>
       </c>
       <c r="G8">
         <v>0.262</v>
@@ -1931,28 +1931,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M8">
-        <v>0.06198971999999999</v>
+        <v>0.07232133999999998</v>
       </c>
       <c r="N8">
-        <v>8.29801028</v>
+        <v>8.287678659999999</v>
       </c>
       <c r="O8">
-        <v>2.904303598</v>
+        <v>2.900687531</v>
       </c>
       <c r="P8">
-        <v>5.393706681999999</v>
+        <v>5.386991129</v>
       </c>
       <c r="Q8">
-        <v>7.033706682</v>
+        <v>7.026991129000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2001584664108345</v>
+        <v>0.2012604577248485</v>
       </c>
       <c r="T8">
-        <v>0.7584205954087608</v>
+        <v>0.7638350888793385</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>134.8610705129819</v>
+        <v>115.5952032968416</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1894608756841091</v>
+        <v>0.1888110929420339</v>
       </c>
       <c r="C9">
-        <v>21.03502504595723</v>
+        <v>20.9305417686059</v>
       </c>
       <c r="D9">
-        <v>22.21082504595723</v>
+        <v>22.3117417686059</v>
       </c>
       <c r="E9">
-        <v>-10.6622</v>
+        <v>-10.4568</v>
       </c>
       <c r="F9">
-        <v>1.4378</v>
+        <v>1.6432</v>
       </c>
       <c r="G9">
         <v>0.262</v>
@@ -2013,28 +2013,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M9">
-        <v>0.07232134</v>
+        <v>0.08265296</v>
       </c>
       <c r="N9">
-        <v>8.287678659999999</v>
+        <v>8.277347039999999</v>
       </c>
       <c r="O9">
-        <v>2.900687531</v>
+        <v>2.897071463999999</v>
       </c>
       <c r="P9">
-        <v>5.386991129</v>
+        <v>5.380275575999999</v>
       </c>
       <c r="Q9">
-        <v>7.026991129000001</v>
+        <v>7.020275576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2012604577248485</v>
+        <v>0.202386405371776</v>
       </c>
       <c r="T9">
-        <v>0.7638350888793385</v>
+        <v>0.7693672887297114</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>115.5952032968416</v>
+        <v>101.1458028847364</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1888110929420339</v>
+        <v>0.1881613101999587</v>
       </c>
       <c r="C10">
-        <v>20.9305417686059</v>
+        <v>20.82697972392195</v>
       </c>
       <c r="D10">
-        <v>22.3117417686059</v>
+        <v>22.41357972392195</v>
       </c>
       <c r="E10">
-        <v>-10.4568</v>
+        <v>-10.2514</v>
       </c>
       <c r="F10">
-        <v>1.6432</v>
+        <v>1.8486</v>
       </c>
       <c r="G10">
         <v>0.262</v>
@@ -2095,28 +2095,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M10">
-        <v>0.08265296</v>
+        <v>0.09298457999999998</v>
       </c>
       <c r="N10">
-        <v>8.277347039999999</v>
+        <v>8.26701542</v>
       </c>
       <c r="O10">
-        <v>2.897071463999999</v>
+        <v>2.893455397</v>
       </c>
       <c r="P10">
-        <v>5.380275575999999</v>
+        <v>5.373560023</v>
       </c>
       <c r="Q10">
-        <v>7.020275576</v>
+        <v>7.013560023</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.202386405371776</v>
+        <v>0.2035370991208338</v>
       </c>
       <c r="T10">
-        <v>0.7693672887297114</v>
+        <v>0.7750210753899828</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>101.1458028847364</v>
+        <v>89.9073803419879</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1881613101999587</v>
+        <v>0.1875115274578835</v>
       </c>
       <c r="C11">
-        <v>20.82697972392195</v>
+        <v>20.7243515841509</v>
       </c>
       <c r="D11">
-        <v>22.41357972392195</v>
+        <v>22.5163515841509</v>
       </c>
       <c r="E11">
-        <v>-10.2514</v>
+        <v>-10.046</v>
       </c>
       <c r="F11">
-        <v>1.8486</v>
+        <v>2.054</v>
       </c>
       <c r="G11">
         <v>0.262</v>
@@ -2177,28 +2177,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M11">
-        <v>0.09298457999999998</v>
+        <v>0.1033162</v>
       </c>
       <c r="N11">
-        <v>8.26701542</v>
+        <v>8.256683799999999</v>
       </c>
       <c r="O11">
-        <v>2.893455397</v>
+        <v>2.88983933</v>
       </c>
       <c r="P11">
-        <v>5.373560023</v>
+        <v>5.36684447</v>
       </c>
       <c r="Q11">
-        <v>7.013560023</v>
+        <v>7.006844470000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2035370991208338</v>
+        <v>0.2047133638420928</v>
       </c>
       <c r="T11">
-        <v>0.7750210753899828</v>
+        <v>0.7808005017538155</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>89.9073803419879</v>
+        <v>80.9166423077891</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1875115274578835</v>
+        <v>0.1868617447158083</v>
       </c>
       <c r="C12">
-        <v>20.7243515841509</v>
+        <v>20.62267025503048</v>
       </c>
       <c r="D12">
-        <v>22.5163515841509</v>
+        <v>22.62007025503048</v>
       </c>
       <c r="E12">
-        <v>-10.046</v>
+        <v>-9.8406</v>
       </c>
       <c r="F12">
-        <v>2.054</v>
+        <v>2.2594</v>
       </c>
       <c r="G12">
         <v>0.262</v>
@@ -2259,28 +2259,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M12">
-        <v>0.1033162</v>
+        <v>0.11364782</v>
       </c>
       <c r="N12">
-        <v>8.256683799999999</v>
+        <v>8.246352179999999</v>
       </c>
       <c r="O12">
-        <v>2.88983933</v>
+        <v>2.886223262999999</v>
       </c>
       <c r="P12">
-        <v>5.36684447</v>
+        <v>5.360128916999999</v>
       </c>
       <c r="Q12">
-        <v>7.006844470000001</v>
+        <v>7.000128917</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2047133638420928</v>
+        <v>0.2059160614784363</v>
       </c>
       <c r="T12">
-        <v>0.7808005017538155</v>
+        <v>0.7867098028673976</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>80.9166423077891</v>
+        <v>73.56058391617191</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1868617447158083</v>
+        <v>0.186211961973733</v>
       </c>
       <c r="C13">
-        <v>20.62267025503048</v>
+        <v>20.52194888119339</v>
       </c>
       <c r="D13">
-        <v>22.62007025503048</v>
+        <v>22.72474888119339</v>
       </c>
       <c r="E13">
-        <v>-9.8406</v>
+        <v>-9.635199999999999</v>
       </c>
       <c r="F13">
-        <v>2.2594</v>
+        <v>2.4648</v>
       </c>
       <c r="G13">
         <v>0.262</v>
@@ -2341,28 +2341,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M13">
-        <v>0.11364782</v>
+        <v>0.12397944</v>
       </c>
       <c r="N13">
-        <v>8.246352179999999</v>
+        <v>8.23602056</v>
       </c>
       <c r="O13">
-        <v>2.886223262999999</v>
+        <v>2.882607196</v>
       </c>
       <c r="P13">
-        <v>5.360128916999999</v>
+        <v>5.353413364</v>
       </c>
       <c r="Q13">
-        <v>7.000128917</v>
+        <v>6.993413364</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2059160614784363</v>
+        <v>0.2071460931519694</v>
       </c>
       <c r="T13">
-        <v>0.7867098028673976</v>
+        <v>0.7927534062790152</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>73.56058391617191</v>
+        <v>67.43053525649093</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.186211961973733</v>
+        <v>0.1855621792316578</v>
       </c>
       <c r="C14">
-        <v>20.52194888119339</v>
+        <v>20.42220085172053</v>
       </c>
       <c r="D14">
-        <v>22.72474888119339</v>
+        <v>22.83040085172053</v>
       </c>
       <c r="E14">
-        <v>-9.635199999999999</v>
+        <v>-9.4298</v>
       </c>
       <c r="F14">
-        <v>2.4648</v>
+        <v>2.6702</v>
       </c>
       <c r="G14">
         <v>0.262</v>
@@ -2423,28 +2423,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M14">
-        <v>0.12397944</v>
+        <v>0.13431106</v>
       </c>
       <c r="N14">
-        <v>8.23602056</v>
+        <v>8.22568894</v>
       </c>
       <c r="O14">
-        <v>2.882607196</v>
+        <v>2.878991129</v>
       </c>
       <c r="P14">
-        <v>5.353413364</v>
+        <v>5.346697811</v>
       </c>
       <c r="Q14">
-        <v>6.993413364</v>
+        <v>6.986697811000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2071460931519694</v>
+        <v>0.2084044014156986</v>
       </c>
       <c r="T14">
-        <v>0.7927534062790152</v>
+        <v>0.7989359431023945</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>67.43053525649093</v>
+        <v>62.24357100599162</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1855621792316578</v>
+        <v>0.1849123964895826</v>
       </c>
       <c r="C15">
-        <v>20.42220085172053</v>
+        <v>20.3234398058501</v>
       </c>
       <c r="D15">
-        <v>22.83040085172053</v>
+        <v>22.9370398058501</v>
       </c>
       <c r="E15">
-        <v>-9.4298</v>
+        <v>-9.224399999999999</v>
       </c>
       <c r="F15">
-        <v>2.6702</v>
+        <v>2.8756</v>
       </c>
       <c r="G15">
         <v>0.262</v>
@@ -2505,28 +2505,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M15">
-        <v>0.13431106</v>
+        <v>0.14464268</v>
       </c>
       <c r="N15">
-        <v>8.22568894</v>
+        <v>8.215357319999999</v>
       </c>
       <c r="O15">
-        <v>2.878991129</v>
+        <v>2.875375061999999</v>
       </c>
       <c r="P15">
-        <v>5.346697811</v>
+        <v>5.339982257999999</v>
       </c>
       <c r="Q15">
-        <v>6.986697811000001</v>
+        <v>6.979982258</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2084044014156986</v>
+        <v>0.2096919726623054</v>
       </c>
       <c r="T15">
-        <v>0.7989359431023945</v>
+        <v>0.8052622598518988</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>62.24357100599162</v>
+        <v>57.79760164842078</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1849123964895826</v>
+        <v>0.1842626137475074</v>
       </c>
       <c r="C16">
-        <v>20.3234398058501</v>
+        <v>20.22567963884728</v>
       </c>
       <c r="D16">
-        <v>22.9370398058501</v>
+        <v>23.04467963884728</v>
       </c>
       <c r="E16">
-        <v>-9.224399999999999</v>
+        <v>-9.018999999999998</v>
       </c>
       <c r="F16">
-        <v>2.8756</v>
+        <v>3.081</v>
       </c>
       <c r="G16">
         <v>0.262</v>
@@ -2587,28 +2587,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M16">
-        <v>0.14464268</v>
+        <v>0.1549743</v>
       </c>
       <c r="N16">
-        <v>8.215357319999999</v>
+        <v>8.2050257</v>
       </c>
       <c r="O16">
-        <v>2.875375061999999</v>
+        <v>2.871758995</v>
       </c>
       <c r="P16">
-        <v>5.339982257999999</v>
+        <v>5.333266705</v>
       </c>
       <c r="Q16">
-        <v>6.979982258</v>
+        <v>6.973266705</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2096919726623054</v>
+        <v>0.2110098397029499</v>
       </c>
       <c r="T16">
-        <v>0.8052622598518988</v>
+        <v>0.8117374311131561</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>57.79760164842078</v>
+        <v>53.94442820519273</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1842626137475074</v>
+        <v>0.1836128310054321</v>
       </c>
       <c r="C17">
-        <v>20.22567963884728</v>
+        <v>20.12893450804001</v>
       </c>
       <c r="D17">
-        <v>23.04467963884728</v>
+        <v>23.15333450804001</v>
       </c>
       <c r="E17">
-        <v>-9.019</v>
+        <v>-8.813599999999999</v>
       </c>
       <c r="F17">
-        <v>3.081</v>
+        <v>3.2864</v>
       </c>
       <c r="G17">
         <v>0.262</v>
@@ -2669,28 +2669,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M17">
-        <v>0.1549743</v>
+        <v>0.16530592</v>
       </c>
       <c r="N17">
-        <v>8.2050257</v>
+        <v>8.19469408</v>
       </c>
       <c r="O17">
-        <v>2.871758995</v>
+        <v>2.868142928</v>
       </c>
       <c r="P17">
-        <v>5.333266705</v>
+        <v>5.326551152</v>
       </c>
       <c r="Q17">
-        <v>6.973266705</v>
+        <v>6.966551152000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2110098397029499</v>
+        <v>0.2123590845302764</v>
       </c>
       <c r="T17">
-        <v>0.8117374311131561</v>
+        <v>0.818366773118729</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>53.94442820519274</v>
+        <v>50.57290144236818</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1836128310054321</v>
+        <v>0.1829630482633569</v>
       </c>
       <c r="C18">
-        <v>20.12893450804001</v>
+        <v>20.03321883902639</v>
       </c>
       <c r="D18">
-        <v>23.15333450804001</v>
+        <v>23.26301883902639</v>
       </c>
       <c r="E18">
-        <v>-8.813599999999999</v>
+        <v>-8.6082</v>
       </c>
       <c r="F18">
-        <v>3.2864</v>
+        <v>3.4918</v>
       </c>
       <c r="G18">
         <v>0.262</v>
@@ -2751,28 +2751,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M18">
-        <v>0.16530592</v>
+        <v>0.17563754</v>
       </c>
       <c r="N18">
-        <v>8.19469408</v>
+        <v>8.184362459999999</v>
       </c>
       <c r="O18">
-        <v>2.868142928</v>
+        <v>2.864526860999999</v>
       </c>
       <c r="P18">
-        <v>5.326551152</v>
+        <v>5.319835598999999</v>
       </c>
       <c r="Q18">
-        <v>6.966551152000001</v>
+        <v>6.959835599</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2123590845302764</v>
+        <v>0.2137408412811529</v>
       </c>
       <c r="T18">
-        <v>0.818366773118729</v>
+        <v>0.8251558583051591</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>50.57290144236818</v>
+        <v>47.59802488693477</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1829630482633569</v>
+        <v>0.1823132655212817</v>
       </c>
       <c r="C19">
-        <v>20.03321883902639</v>
+        <v>19.93854733205929</v>
       </c>
       <c r="D19">
-        <v>23.26301883902639</v>
+        <v>23.37374733205929</v>
       </c>
       <c r="E19">
-        <v>-8.6082</v>
+        <v>-8.402799999999999</v>
       </c>
       <c r="F19">
-        <v>3.4918</v>
+        <v>3.6972</v>
       </c>
       <c r="G19">
         <v>0.262</v>
@@ -2833,28 +2833,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M19">
-        <v>0.17563754</v>
+        <v>0.18596916</v>
       </c>
       <c r="N19">
-        <v>8.184362459999999</v>
+        <v>8.174030839999999</v>
       </c>
       <c r="O19">
-        <v>2.864526860999999</v>
+        <v>2.860910793999999</v>
       </c>
       <c r="P19">
-        <v>5.319835598999999</v>
+        <v>5.313120046</v>
       </c>
       <c r="Q19">
-        <v>6.959835599</v>
+        <v>6.953120046</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2137408412811529</v>
+        <v>0.2151562994161972</v>
       </c>
       <c r="T19">
-        <v>0.8251558583051591</v>
+        <v>0.8321105309351606</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>47.59802488693477</v>
+        <v>44.95369017099393</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1823132655212817</v>
+        <v>0.1816634827792065</v>
       </c>
       <c r="C20">
-        <v>19.93854733205929</v>
+        <v>19.84493496861413</v>
       </c>
       <c r="D20">
-        <v>23.37374733205928</v>
+        <v>23.48553496861413</v>
       </c>
       <c r="E20">
-        <v>-8.402799999999999</v>
+        <v>-8.1974</v>
       </c>
       <c r="F20">
-        <v>3.6972</v>
+        <v>3.9026</v>
       </c>
       <c r="G20">
         <v>0.262</v>
@@ -2915,28 +2915,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M20">
-        <v>0.18596916</v>
+        <v>0.19630078</v>
       </c>
       <c r="N20">
-        <v>8.17403084</v>
+        <v>8.16369922</v>
       </c>
       <c r="O20">
-        <v>2.860910794</v>
+        <v>2.857294727</v>
       </c>
       <c r="P20">
-        <v>5.313120046</v>
+        <v>5.306404493</v>
       </c>
       <c r="Q20">
-        <v>6.953120046</v>
+        <v>6.946404493000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2151562994161972</v>
+        <v>0.2166067071348228</v>
       </c>
       <c r="T20">
-        <v>0.8321105309351606</v>
+        <v>0.8392369238770143</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>44.95369017099395</v>
+        <v>42.58770647778374</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1816634827792065</v>
+        <v>0.1810137000371313</v>
       </c>
       <c r="C21">
-        <v>19.84493496861413</v>
+        <v>19.75239701814624</v>
       </c>
       <c r="D21">
-        <v>23.48553496861413</v>
+        <v>23.59839701814624</v>
       </c>
       <c r="E21">
-        <v>-8.1974</v>
+        <v>-7.992</v>
       </c>
       <c r="F21">
-        <v>3.9026</v>
+        <v>4.108</v>
       </c>
       <c r="G21">
         <v>0.262</v>
@@ -2997,28 +2997,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M21">
-        <v>0.19630078</v>
+        <v>0.2066324</v>
       </c>
       <c r="N21">
-        <v>8.16369922</v>
+        <v>8.153367599999999</v>
       </c>
       <c r="O21">
-        <v>2.857294727</v>
+        <v>2.853678659999999</v>
       </c>
       <c r="P21">
-        <v>5.306404493</v>
+        <v>5.299688939999999</v>
       </c>
       <c r="Q21">
-        <v>6.946404493000001</v>
+        <v>6.93968894</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2166067071348228</v>
+        <v>0.2180933750464141</v>
       </c>
       <c r="T21">
-        <v>0.8392369238770143</v>
+        <v>0.8465414766424141</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>42.58770647778374</v>
+        <v>40.45832115389455</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1810137000371313</v>
+        <v>0.180363917295056</v>
       </c>
       <c r="C22">
-        <v>19.75239701814624</v>
+        <v>19.66094904504368</v>
       </c>
       <c r="D22">
-        <v>23.59839701814624</v>
+        <v>23.71234904504368</v>
       </c>
       <c r="E22">
-        <v>-7.992</v>
+        <v>-7.786599999999999</v>
       </c>
       <c r="F22">
-        <v>4.108</v>
+        <v>4.313400000000001</v>
       </c>
       <c r="G22">
         <v>0.262</v>
@@ -3079,28 +3079,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M22">
-        <v>0.2066324</v>
+        <v>0.21696402</v>
       </c>
       <c r="N22">
-        <v>8.153367599999999</v>
+        <v>8.143035979999999</v>
       </c>
       <c r="O22">
-        <v>2.853678659999999</v>
+        <v>2.850062592999999</v>
       </c>
       <c r="P22">
-        <v>5.299688939999999</v>
+        <v>5.292973387</v>
       </c>
       <c r="Q22">
-        <v>6.93968894</v>
+        <v>6.932973387000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2180933750464141</v>
+        <v>0.2196176801203241</v>
       </c>
       <c r="T22">
-        <v>0.8465414766424141</v>
+        <v>0.8540309547942797</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>40.45832115389455</v>
+        <v>38.53173443228052</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.180363917295056</v>
+        <v>0.1797141345529808</v>
       </c>
       <c r="C23">
-        <v>19.66094904504368</v>
+        <v>19.57060691578276</v>
       </c>
       <c r="D23">
-        <v>23.71234904504368</v>
+        <v>23.82740691578276</v>
       </c>
       <c r="E23">
-        <v>-7.7866</v>
+        <v>-7.5812</v>
       </c>
       <c r="F23">
-        <v>4.3134</v>
+        <v>4.5188</v>
       </c>
       <c r="G23">
         <v>0.262</v>
@@ -3161,28 +3161,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M23">
-        <v>0.21696402</v>
+        <v>0.22729564</v>
       </c>
       <c r="N23">
-        <v>8.143035979999999</v>
+        <v>8.13270436</v>
       </c>
       <c r="O23">
-        <v>2.850062592999999</v>
+        <v>2.846446526</v>
       </c>
       <c r="P23">
-        <v>5.292973387</v>
+        <v>5.286257834000001</v>
       </c>
       <c r="Q23">
-        <v>6.932973387000001</v>
+        <v>6.926257834000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2196176801203241</v>
+        <v>0.221181069939719</v>
       </c>
       <c r="T23">
-        <v>0.8540309547942797</v>
+        <v>0.8617124708474753</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>38.53173443228052</v>
+        <v>36.78029195808596</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1797141345529808</v>
+        <v>0.1790643518109056</v>
       </c>
       <c r="C24">
-        <v>19.57060691578276</v>
+        <v>19.48138680629278</v>
       </c>
       <c r="D24">
-        <v>23.82740691578276</v>
+        <v>23.94358680629278</v>
       </c>
       <c r="E24">
-        <v>-7.5812</v>
+        <v>-7.3758</v>
       </c>
       <c r="F24">
-        <v>4.5188</v>
+        <v>4.7242</v>
       </c>
       <c r="G24">
         <v>0.262</v>
@@ -3243,28 +3243,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M24">
-        <v>0.22729564</v>
+        <v>0.23762726</v>
       </c>
       <c r="N24">
-        <v>8.13270436</v>
+        <v>8.122372739999999</v>
       </c>
       <c r="O24">
-        <v>2.846446526</v>
+        <v>2.842830459</v>
       </c>
       <c r="P24">
-        <v>5.286257834000001</v>
+        <v>5.279542280999999</v>
       </c>
       <c r="Q24">
-        <v>6.926257834000001</v>
+        <v>6.919542281</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.221181069939719</v>
+        <v>0.2227850672868903</v>
       </c>
       <c r="T24">
-        <v>0.8617124708474753</v>
+        <v>0.8695935067981564</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>36.78029195808596</v>
+        <v>35.18114882947352</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1790643518109056</v>
+        <v>0.1784145690688304</v>
       </c>
       <c r="C25">
-        <v>19.48138680629278</v>
+        <v>19.39330520953725</v>
       </c>
       <c r="D25">
-        <v>23.94358680629278</v>
+        <v>24.06090520953725</v>
       </c>
       <c r="E25">
-        <v>-7.3758</v>
+        <v>-7.1704</v>
       </c>
       <c r="F25">
-        <v>4.7242</v>
+        <v>4.9296</v>
       </c>
       <c r="G25">
         <v>0.262</v>
@@ -3325,28 +3325,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M25">
-        <v>0.23762726</v>
+        <v>0.24795888</v>
       </c>
       <c r="N25">
-        <v>8.122372739999999</v>
+        <v>8.112041119999999</v>
       </c>
       <c r="O25">
-        <v>2.842830459</v>
+        <v>2.839214391999999</v>
       </c>
       <c r="P25">
-        <v>5.279542280999999</v>
+        <v>5.272826728</v>
       </c>
       <c r="Q25">
-        <v>6.919542281</v>
+        <v>6.912826728000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2227850672868903</v>
+        <v>0.2244312750905662</v>
       </c>
       <c r="T25">
-        <v>0.8695935067981564</v>
+        <v>0.8776819384317501</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>35.18114882947352</v>
+        <v>33.71526762824546</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1784145690688304</v>
+        <v>0.1777647863267551</v>
       </c>
       <c r="C26">
-        <v>19.39330520953725</v>
+        <v>19.30637894331918</v>
       </c>
       <c r="D26">
-        <v>24.06090520953725</v>
+        <v>24.17937894331918</v>
       </c>
       <c r="E26">
-        <v>-7.1704</v>
+        <v>-6.965</v>
       </c>
       <c r="F26">
-        <v>4.9296</v>
+        <v>5.135</v>
       </c>
       <c r="G26">
         <v>0.262</v>
@@ -3407,28 +3407,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M26">
-        <v>0.24795888</v>
+        <v>0.2582905</v>
       </c>
       <c r="N26">
-        <v>8.112041119999999</v>
+        <v>8.1017095</v>
       </c>
       <c r="O26">
-        <v>2.839214391999999</v>
+        <v>2.835598325</v>
       </c>
       <c r="P26">
-        <v>5.272826728</v>
+        <v>5.266111175000001</v>
       </c>
       <c r="Q26">
-        <v>6.912826728000001</v>
+        <v>6.906111175000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2244312750905662</v>
+        <v>0.2261213817690068</v>
       </c>
       <c r="T26">
-        <v>0.8776819384317501</v>
+        <v>0.8859860615755732</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>33.71526762824546</v>
+        <v>32.36665692311564</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1777647863267551</v>
+        <v>0.1771150035846799</v>
       </c>
       <c r="C27">
-        <v>19.30637894331918</v>
+        <v>19.22062515831803</v>
       </c>
       <c r="D27">
-        <v>24.17937894331918</v>
+        <v>24.29902515831803</v>
       </c>
       <c r="E27">
-        <v>-6.965</v>
+        <v>-6.7596</v>
       </c>
       <c r="F27">
-        <v>5.135</v>
+        <v>5.3404</v>
       </c>
       <c r="G27">
         <v>0.262</v>
@@ -3489,28 +3489,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M27">
-        <v>0.2582905</v>
+        <v>0.26862212</v>
       </c>
       <c r="N27">
-        <v>8.1017095</v>
+        <v>8.09137788</v>
       </c>
       <c r="O27">
-        <v>2.835598325</v>
+        <v>2.831982258</v>
       </c>
       <c r="P27">
-        <v>5.266111175000001</v>
+        <v>5.259395622</v>
       </c>
       <c r="Q27">
-        <v>6.906111175000001</v>
+        <v>6.899395622</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2261213817690068</v>
+        <v>0.2278571670063242</v>
       </c>
       <c r="T27">
-        <v>0.8859860615755732</v>
+        <v>0.8945146204800399</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>32.36665692311564</v>
+        <v>31.12178550299581</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1771150035846799</v>
+        <v>0.1764652208426047</v>
       </c>
       <c r="C28">
-        <v>19.22062515831803</v>
+        <v>19.13606134636646</v>
       </c>
       <c r="D28">
-        <v>24.29902515831803</v>
+        <v>24.41986134636646</v>
       </c>
       <c r="E28">
-        <v>-6.7596</v>
+        <v>-6.5542</v>
       </c>
       <c r="F28">
-        <v>5.3404</v>
+        <v>5.5458</v>
       </c>
       <c r="G28">
         <v>0.262</v>
@@ -3571,28 +3571,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M28">
-        <v>0.26862212</v>
+        <v>0.27895374</v>
       </c>
       <c r="N28">
-        <v>8.09137788</v>
+        <v>8.081046259999999</v>
       </c>
       <c r="O28">
-        <v>2.831982258</v>
+        <v>2.828366190999999</v>
       </c>
       <c r="P28">
-        <v>5.259395622</v>
+        <v>5.252680069</v>
       </c>
       <c r="Q28">
-        <v>6.899395622</v>
+        <v>6.892680069000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2278571670063242</v>
+        <v>0.2296405080035681</v>
       </c>
       <c r="T28">
-        <v>0.8945146204800399</v>
+        <v>0.9032768385325745</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>31.12178550299581</v>
+        <v>29.96912678066262</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1764652208426047</v>
+        <v>0.1758154381005294</v>
       </c>
       <c r="C29">
-        <v>19.13606134636646</v>
+        <v>19.05270534897536</v>
       </c>
       <c r="D29">
-        <v>24.41986134636646</v>
+        <v>24.54190534897536</v>
       </c>
       <c r="E29">
-        <v>-6.5542</v>
+        <v>-6.3488</v>
       </c>
       <c r="F29">
-        <v>5.5458</v>
+        <v>5.7512</v>
       </c>
       <c r="G29">
         <v>0.262</v>
@@ -3653,28 +3653,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M29">
-        <v>0.27895374</v>
+        <v>0.28928536</v>
       </c>
       <c r="N29">
-        <v>8.081046259999999</v>
+        <v>8.07071464</v>
       </c>
       <c r="O29">
-        <v>2.828366190999999</v>
+        <v>2.824750124</v>
       </c>
       <c r="P29">
-        <v>5.252680069</v>
+        <v>5.245964516000001</v>
       </c>
       <c r="Q29">
-        <v>6.892680069000001</v>
+        <v>6.885964516000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2296405080035681</v>
+        <v>0.2314733862507353</v>
       </c>
       <c r="T29">
-        <v>0.9032768385325745</v>
+        <v>0.9122824515310125</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>29.96912678066262</v>
+        <v>28.89880082421039</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1758154381005294</v>
+        <v>0.1751656553584542</v>
       </c>
       <c r="C30">
-        <v>19.05270534897536</v>
+        <v>18.9705753661157</v>
       </c>
       <c r="D30">
-        <v>24.54190534897536</v>
+        <v>24.6651753661157</v>
       </c>
       <c r="E30">
-        <v>-6.3488</v>
+        <v>-6.143399999999999</v>
       </c>
       <c r="F30">
-        <v>5.7512</v>
+        <v>5.956600000000001</v>
       </c>
       <c r="G30">
         <v>0.262</v>
@@ -3735,28 +3735,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M30">
-        <v>0.28928536</v>
+        <v>0.29961698</v>
       </c>
       <c r="N30">
-        <v>8.07071464</v>
+        <v>8.06038302</v>
       </c>
       <c r="O30">
-        <v>2.824750124</v>
+        <v>2.821134057</v>
       </c>
       <c r="P30">
-        <v>5.245964516000001</v>
+        <v>5.239248963</v>
       </c>
       <c r="Q30">
-        <v>6.885964516000001</v>
+        <v>6.879248963</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2314733862507353</v>
+        <v>0.2333578948710623</v>
       </c>
       <c r="T30">
-        <v>0.9122824515310125</v>
+        <v>0.9215417437688432</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>28.89880082421039</v>
+        <v>27.90229045096175</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1751656553584542</v>
+        <v>0.174515872616379</v>
       </c>
       <c r="C31">
-        <v>18.9705753661157</v>
+        <v>18.88968996526641</v>
       </c>
       <c r="D31">
-        <v>24.6651753661157</v>
+        <v>24.7896899652664</v>
       </c>
       <c r="E31">
-        <v>-6.143400000000001</v>
+        <v>-5.938</v>
       </c>
       <c r="F31">
-        <v>5.956599999999999</v>
+        <v>6.162</v>
       </c>
       <c r="G31">
         <v>0.262</v>
@@ -3817,28 +3817,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M31">
-        <v>0.2996169799999999</v>
+        <v>0.3099486</v>
       </c>
       <c r="N31">
-        <v>8.06038302</v>
+        <v>8.050051399999999</v>
       </c>
       <c r="O31">
-        <v>2.821134057</v>
+        <v>2.817517989999999</v>
       </c>
       <c r="P31">
-        <v>5.239248963</v>
+        <v>5.23253341</v>
       </c>
       <c r="Q31">
-        <v>6.879248963</v>
+        <v>6.872533410000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2333578948710623</v>
+        <v>0.2352962465948271</v>
       </c>
       <c r="T31">
-        <v>0.9215417437688432</v>
+        <v>0.9310655872134691</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>27.90229045096176</v>
+        <v>26.97221410259637</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.174515872616379</v>
+        <v>0.1738660898743037</v>
       </c>
       <c r="C32">
-        <v>18.88968996526641</v>
+        <v>18.81006809073768</v>
       </c>
       <c r="D32">
-        <v>24.7896899652664</v>
+        <v>24.91546809073768</v>
       </c>
       <c r="E32">
-        <v>-5.938</v>
+        <v>-5.7326</v>
       </c>
       <c r="F32">
-        <v>6.162</v>
+        <v>6.3674</v>
       </c>
       <c r="G32">
         <v>0.262</v>
@@ -3899,28 +3899,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M32">
-        <v>0.3099486</v>
+        <v>0.32028022</v>
       </c>
       <c r="N32">
-        <v>8.050051399999999</v>
+        <v>8.039719779999999</v>
       </c>
       <c r="O32">
-        <v>2.817517989999999</v>
+        <v>2.813901923</v>
       </c>
       <c r="P32">
-        <v>5.23253341</v>
+        <v>5.225817856999999</v>
       </c>
       <c r="Q32">
-        <v>6.872533410000001</v>
+        <v>6.865817857</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2352962465948271</v>
+        <v>0.2372907824265272</v>
       </c>
       <c r="T32">
-        <v>0.9310655872134691</v>
+        <v>0.9408654840912727</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>26.97221410259637</v>
+        <v>26.10214267993196</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1738660898743037</v>
+        <v>0.1732163071322285</v>
       </c>
       <c r="C33">
-        <v>18.81006809073768</v>
+        <v>18.73172907327961</v>
       </c>
       <c r="D33">
-        <v>24.91546809073768</v>
+        <v>25.04252907327961</v>
       </c>
       <c r="E33">
-        <v>-5.7326</v>
+        <v>-5.5272</v>
       </c>
       <c r="F33">
-        <v>6.3674</v>
+        <v>6.5728</v>
       </c>
       <c r="G33">
         <v>0.262</v>
@@ -3981,28 +3981,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M33">
-        <v>0.32028022</v>
+        <v>0.33061184</v>
       </c>
       <c r="N33">
-        <v>8.039719779999999</v>
+        <v>8.02938816</v>
       </c>
       <c r="O33">
-        <v>2.813901923</v>
+        <v>2.810285856</v>
       </c>
       <c r="P33">
-        <v>5.225817856999999</v>
+        <v>5.219102304</v>
       </c>
       <c r="Q33">
-        <v>6.865817857</v>
+        <v>6.859102304</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2372907824265272</v>
+        <v>0.2393439810768067</v>
       </c>
       <c r="T33">
-        <v>0.9408654840912727</v>
+        <v>0.9509536132301881</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>26.10214267993196</v>
+        <v>25.28645072118409</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1732163071322285</v>
+        <v>0.1725665243901533</v>
       </c>
       <c r="C34">
-        <v>18.73172907327961</v>
+        <v>18.65469263998634</v>
       </c>
       <c r="D34">
-        <v>25.04252907327961</v>
+        <v>25.17089263998634</v>
       </c>
       <c r="E34">
-        <v>-5.5272</v>
+        <v>-5.3218</v>
       </c>
       <c r="F34">
-        <v>6.5728</v>
+        <v>6.7782</v>
       </c>
       <c r="G34">
         <v>0.262</v>
@@ -4063,28 +4063,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M34">
-        <v>0.33061184</v>
+        <v>0.34094346</v>
       </c>
       <c r="N34">
-        <v>8.02938816</v>
+        <v>8.019056539999999</v>
       </c>
       <c r="O34">
-        <v>2.810285856</v>
+        <v>2.806669788999999</v>
       </c>
       <c r="P34">
-        <v>5.219102304</v>
+        <v>5.212386751</v>
       </c>
       <c r="Q34">
-        <v>6.859102304</v>
+        <v>6.852386751000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2393439810768067</v>
+        <v>0.2414584692390348</v>
       </c>
       <c r="T34">
-        <v>0.9509536132301881</v>
+        <v>0.9613428805523546</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>25.28645072118409</v>
+        <v>24.52019463872397</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1725665243901533</v>
+        <v>0.1719167416480781</v>
       </c>
       <c r="C35">
-        <v>18.65469263998634</v>
+        <v>18.57897892450621</v>
       </c>
       <c r="D35">
-        <v>25.17089263998634</v>
+        <v>25.3005789245062</v>
       </c>
       <c r="E35">
-        <v>-5.3218</v>
+        <v>-5.1164</v>
       </c>
       <c r="F35">
-        <v>6.7782</v>
+        <v>6.9836</v>
       </c>
       <c r="G35">
         <v>0.262</v>
@@ -4145,28 +4145,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M35">
-        <v>0.34094346</v>
+        <v>0.35127508</v>
       </c>
       <c r="N35">
-        <v>8.019056539999999</v>
+        <v>8.008724919999999</v>
       </c>
       <c r="O35">
-        <v>2.806669788999999</v>
+        <v>2.803053722</v>
       </c>
       <c r="P35">
-        <v>5.212386751</v>
+        <v>5.205671197999999</v>
       </c>
       <c r="Q35">
-        <v>6.852386751000001</v>
+        <v>6.845671198</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2414584692390348</v>
+        <v>0.2436370328001183</v>
       </c>
       <c r="T35">
-        <v>0.9613428805523546</v>
+        <v>0.9720469741570111</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>24.52019463872397</v>
+        <v>23.79901244346738</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1719167416480781</v>
+        <v>0.1712669589060029</v>
       </c>
       <c r="C36">
-        <v>18.57897892450621</v>
+        <v>18.50460847756943</v>
       </c>
       <c r="D36">
-        <v>25.3005789245062</v>
+        <v>25.43160847756943</v>
       </c>
       <c r="E36">
-        <v>-5.1164</v>
+        <v>-4.911</v>
       </c>
       <c r="F36">
-        <v>6.9836</v>
+        <v>7.189</v>
       </c>
       <c r="G36">
         <v>0.262</v>
@@ -4227,28 +4227,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M36">
-        <v>0.35127508</v>
+        <v>0.3616067</v>
       </c>
       <c r="N36">
-        <v>8.008724919999999</v>
+        <v>7.998393299999999</v>
       </c>
       <c r="O36">
-        <v>2.803053722</v>
+        <v>2.799437655</v>
       </c>
       <c r="P36">
-        <v>5.205671197999999</v>
+        <v>5.198955645</v>
       </c>
       <c r="Q36">
-        <v>6.845671198</v>
+        <v>6.838955645</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2436370328001183</v>
+        <v>0.2458826290861583</v>
       </c>
       <c r="T36">
-        <v>0.9720469741570111</v>
+        <v>0.9830804244879647</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>23.79901244346738</v>
+        <v>23.11904065936831</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1712669589060029</v>
+        <v>0.1706171761639276</v>
       </c>
       <c r="C37">
-        <v>18.50460847756943</v>
+        <v>18.43160227784445</v>
       </c>
       <c r="D37">
-        <v>25.43160847756943</v>
+        <v>25.56400227784445</v>
       </c>
       <c r="E37">
-        <v>-4.911</v>
+        <v>-4.705599999999999</v>
       </c>
       <c r="F37">
-        <v>7.189</v>
+        <v>7.394400000000001</v>
       </c>
       <c r="G37">
         <v>0.262</v>
@@ -4309,28 +4309,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M37">
-        <v>0.3616067</v>
+        <v>0.37193832</v>
       </c>
       <c r="N37">
-        <v>7.998393299999999</v>
+        <v>7.988061679999999</v>
       </c>
       <c r="O37">
-        <v>2.799437655</v>
+        <v>2.795821587999999</v>
       </c>
       <c r="P37">
-        <v>5.198955645</v>
+        <v>5.192240092</v>
       </c>
       <c r="Q37">
-        <v>6.838955645</v>
+        <v>6.832240092000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2458826290861583</v>
+        <v>0.2481984002561369</v>
       </c>
       <c r="T37">
-        <v>0.9830804244879647</v>
+        <v>0.9944586701417606</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>23.11904065936831</v>
+        <v>22.47684508549697</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1706171761639277</v>
+        <v>0.1699673934218524</v>
       </c>
       <c r="C38">
-        <v>18.43160227784445</v>
+        <v>18.35998174313515</v>
       </c>
       <c r="D38">
-        <v>25.56400227784445</v>
+        <v>25.69778174313515</v>
       </c>
       <c r="E38">
-        <v>-4.7056</v>
+        <v>-4.5002</v>
       </c>
       <c r="F38">
-        <v>7.394399999999999</v>
+        <v>7.599799999999999</v>
       </c>
       <c r="G38">
         <v>0.262</v>
@@ -4391,28 +4391,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M38">
-        <v>0.3719383199999999</v>
+        <v>0.3822699399999999</v>
       </c>
       <c r="N38">
-        <v>7.988061679999999</v>
+        <v>7.97773006</v>
       </c>
       <c r="O38">
-        <v>2.795821587999999</v>
+        <v>2.792205521</v>
       </c>
       <c r="P38">
-        <v>5.192240092</v>
+        <v>5.185524539</v>
       </c>
       <c r="Q38">
-        <v>6.832240092000001</v>
+        <v>6.825524539000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2481984002561369</v>
+        <v>0.2505876879711943</v>
       </c>
       <c r="T38">
-        <v>0.9944586701417606</v>
+        <v>1.006198129943296</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>22.47684508549698</v>
+        <v>21.86936278588895</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1699673934218524</v>
+        <v>0.1693176106797772</v>
       </c>
       <c r="C39">
-        <v>18.35998174313515</v>
+        <v>18.28976874193159</v>
       </c>
       <c r="D39">
-        <v>25.69778174313515</v>
+        <v>25.83296874193159</v>
       </c>
       <c r="E39">
-        <v>-4.5002</v>
+        <v>-4.2948</v>
       </c>
       <c r="F39">
-        <v>7.599799999999999</v>
+        <v>7.8052</v>
       </c>
       <c r="G39">
         <v>0.262</v>
@@ -4473,28 +4473,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M39">
-        <v>0.3822699399999999</v>
+        <v>0.39260156</v>
       </c>
       <c r="N39">
-        <v>7.97773006</v>
+        <v>7.967398439999999</v>
       </c>
       <c r="O39">
-        <v>2.792205521</v>
+        <v>2.788589454</v>
       </c>
       <c r="P39">
-        <v>5.185524539</v>
+        <v>5.178808986</v>
       </c>
       <c r="Q39">
-        <v>6.825524539000001</v>
+        <v>6.818808986000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2505876879711943</v>
+        <v>0.2530540494835116</v>
       </c>
       <c r="T39">
-        <v>1.006198129943296</v>
+        <v>1.018316281996494</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>21.86936278588895</v>
+        <v>21.29385323889187</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1693176106797772</v>
+        <v>0.168667827937702</v>
       </c>
       <c r="C40">
-        <v>18.28976874193159</v>
+        <v>18.22098560532714</v>
       </c>
       <c r="D40">
-        <v>25.83296874193159</v>
+        <v>25.96958560532714</v>
       </c>
       <c r="E40">
-        <v>-4.2948</v>
+        <v>-4.089399999999999</v>
       </c>
       <c r="F40">
-        <v>7.8052</v>
+        <v>8.0106</v>
       </c>
       <c r="G40">
         <v>0.262</v>
@@ -4555,28 +4555,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M40">
-        <v>0.39260156</v>
+        <v>0.40293318</v>
       </c>
       <c r="N40">
-        <v>7.967398439999999</v>
+        <v>7.95706682</v>
       </c>
       <c r="O40">
-        <v>2.788589454</v>
+        <v>2.784973387</v>
       </c>
       <c r="P40">
-        <v>5.178808986</v>
+        <v>5.172093433000001</v>
       </c>
       <c r="Q40">
-        <v>6.818808986000001</v>
+        <v>6.812093433000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2530540494835116</v>
+        <v>0.2556012753077082</v>
       </c>
       <c r="T40">
-        <v>1.018316281996494</v>
+        <v>1.030831750510453</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>21.29385323889187</v>
+        <v>20.7478570019972</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.168667827937702</v>
+        <v>0.1680180451956267</v>
       </c>
       <c r="C41">
-        <v>18.22098560532714</v>
+        <v>18.15365513931599</v>
       </c>
       <c r="D41">
-        <v>25.96958560532714</v>
+        <v>26.10765513931599</v>
       </c>
       <c r="E41">
-        <v>-4.089399999999999</v>
+        <v>-3.884</v>
       </c>
       <c r="F41">
-        <v>8.0106</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="G41">
         <v>0.262</v>
@@ -4637,28 +4637,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M41">
-        <v>0.40293318</v>
+        <v>0.4132647999999999</v>
       </c>
       <c r="N41">
-        <v>7.95706682</v>
+        <v>7.946735199999999</v>
       </c>
       <c r="O41">
-        <v>2.784973387</v>
+        <v>2.78135732</v>
       </c>
       <c r="P41">
-        <v>5.172093433000001</v>
+        <v>5.165377879999999</v>
       </c>
       <c r="Q41">
-        <v>6.812093433000001</v>
+        <v>6.80537788</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2556012753077082</v>
+        <v>0.2582334086593779</v>
       </c>
       <c r="T41">
-        <v>1.030831750510453</v>
+        <v>1.043764401308209</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>20.7478570019972</v>
+        <v>20.22916057694728</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1680180451956267</v>
+        <v>0.1673682624535515</v>
       </c>
       <c r="C42">
-        <v>18.15365513931599</v>
+        <v>18.08780063748465</v>
       </c>
       <c r="D42">
-        <v>26.10765513931599</v>
+        <v>26.24720063748465</v>
       </c>
       <c r="E42">
-        <v>-3.884</v>
+        <v>-3.678599999999999</v>
       </c>
       <c r="F42">
-        <v>8.215999999999999</v>
+        <v>8.4214</v>
       </c>
       <c r="G42">
         <v>0.262</v>
@@ -4719,28 +4719,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M42">
-        <v>0.4132647999999999</v>
+        <v>0.42359642</v>
       </c>
       <c r="N42">
-        <v>7.946735199999999</v>
+        <v>7.936403579999999</v>
       </c>
       <c r="O42">
-        <v>2.78135732</v>
+        <v>2.777741253</v>
       </c>
       <c r="P42">
-        <v>5.165377879999999</v>
+        <v>5.158662327</v>
       </c>
       <c r="Q42">
-        <v>6.80537788</v>
+        <v>6.798662327000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2582334086593779</v>
+        <v>0.2609547668704263</v>
       </c>
       <c r="T42">
-        <v>1.043764401308209</v>
+        <v>1.057135447048263</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>20.22916057694728</v>
+        <v>19.73576641653393</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1673682624535515</v>
+        <v>0.1667184797114763</v>
       </c>
       <c r="C43">
-        <v>18.08780063748465</v>
+        <v>18.02344589411307</v>
       </c>
       <c r="D43">
-        <v>26.24720063748465</v>
+        <v>26.38824589411307</v>
       </c>
       <c r="E43">
-        <v>-3.678599999999999</v>
+        <v>-3.473199999999999</v>
       </c>
       <c r="F43">
-        <v>8.4214</v>
+        <v>8.626800000000001</v>
       </c>
       <c r="G43">
         <v>0.262</v>
@@ -4801,28 +4801,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M43">
-        <v>0.42359642</v>
+        <v>0.43392804</v>
       </c>
       <c r="N43">
-        <v>7.936403579999999</v>
+        <v>7.92607196</v>
       </c>
       <c r="O43">
-        <v>2.777741253</v>
+        <v>2.774125186</v>
       </c>
       <c r="P43">
-        <v>5.158662327</v>
+        <v>5.151946774000001</v>
       </c>
       <c r="Q43">
-        <v>6.798662327000001</v>
+        <v>6.791946774000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2609547668704263</v>
+        <v>0.2637699650197867</v>
       </c>
       <c r="T43">
-        <v>1.057135447048263</v>
+        <v>1.070967563331078</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>19.73576641653393</v>
+        <v>19.26586721614026</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1667184797114763</v>
+        <v>0.1660686969694011</v>
       </c>
       <c r="C44">
-        <v>18.02344589411307</v>
+        <v>17.96061521770019</v>
       </c>
       <c r="D44">
-        <v>26.38824589411307</v>
+        <v>26.53081521770019</v>
       </c>
       <c r="E44">
-        <v>-3.4732</v>
+        <v>-3.267799999999999</v>
       </c>
       <c r="F44">
-        <v>8.626799999999999</v>
+        <v>8.8322</v>
       </c>
       <c r="G44">
         <v>0.262</v>
@@ -4883,28 +4883,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M44">
-        <v>0.43392804</v>
+        <v>0.44425966</v>
       </c>
       <c r="N44">
-        <v>7.92607196</v>
+        <v>7.915740339999999</v>
       </c>
       <c r="O44">
-        <v>2.774125186</v>
+        <v>2.770509119</v>
       </c>
       <c r="P44">
-        <v>5.151946774000001</v>
+        <v>5.145231221</v>
       </c>
       <c r="Q44">
-        <v>6.791946774000001</v>
+        <v>6.785231221</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2637699650197867</v>
+        <v>0.2666839420515808</v>
       </c>
       <c r="T44">
-        <v>1.070967563331078</v>
+        <v>1.085285017027324</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>19.26586721614026</v>
+        <v>18.81782379250909</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1660686969694011</v>
+        <v>0.1654189142273259</v>
       </c>
       <c r="C45">
-        <v>17.96061521770019</v>
+        <v>17.89933344493043</v>
       </c>
       <c r="D45">
-        <v>26.53081521770019</v>
+        <v>26.67493344493043</v>
       </c>
       <c r="E45">
-        <v>-3.267799999999999</v>
+        <v>-3.0624</v>
       </c>
       <c r="F45">
-        <v>8.8322</v>
+        <v>9.037599999999999</v>
       </c>
       <c r="G45">
         <v>0.262</v>
@@ -4965,28 +4965,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M45">
-        <v>0.44425966</v>
+        <v>0.4545912799999999</v>
       </c>
       <c r="N45">
-        <v>7.915740339999999</v>
+        <v>7.90540872</v>
       </c>
       <c r="O45">
-        <v>2.770509119</v>
+        <v>2.766893052</v>
       </c>
       <c r="P45">
-        <v>5.145231221</v>
+        <v>5.138515668</v>
       </c>
       <c r="Q45">
-        <v>6.785231221</v>
+        <v>6.778515668000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2666839420515808</v>
+        <v>0.2697019896916533</v>
       </c>
       <c r="T45">
-        <v>1.085285017027324</v>
+        <v>1.100113808355579</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>18.81782379250909</v>
+        <v>18.39014597904298</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1654189142273259</v>
+        <v>0.1647691314852506</v>
       </c>
       <c r="C46">
-        <v>17.89933344493043</v>
+        <v>17.83962595509782</v>
       </c>
       <c r="D46">
-        <v>26.67493344493043</v>
+        <v>26.82062595509782</v>
       </c>
       <c r="E46">
-        <v>-3.0624</v>
+        <v>-2.856999999999999</v>
       </c>
       <c r="F46">
-        <v>9.037599999999999</v>
+        <v>9.243</v>
       </c>
       <c r="G46">
         <v>0.262</v>
@@ -5047,28 +5047,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M46">
-        <v>0.4545912799999999</v>
+        <v>0.4649229</v>
       </c>
       <c r="N46">
-        <v>7.90540872</v>
+        <v>7.895077099999999</v>
       </c>
       <c r="O46">
-        <v>2.766893052</v>
+        <v>2.763276985</v>
       </c>
       <c r="P46">
-        <v>5.138515668</v>
+        <v>5.131800114999999</v>
       </c>
       <c r="Q46">
-        <v>6.778515668000001</v>
+        <v>6.771800115</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2697019896916533</v>
+        <v>0.2728297845186374</v>
       </c>
       <c r="T46">
-        <v>1.100113808355579</v>
+        <v>1.115481828459408</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>18.39014597904298</v>
+        <v>17.98147606839758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1647691314852506</v>
+        <v>0.1641193487431754</v>
       </c>
       <c r="C47">
-        <v>17.83962595509782</v>
+        <v>17.78151868500547</v>
       </c>
       <c r="D47">
-        <v>26.82062595509782</v>
+        <v>26.96791868500547</v>
       </c>
       <c r="E47">
-        <v>-2.856999999999999</v>
+        <v>-2.6516</v>
       </c>
       <c r="F47">
-        <v>9.243</v>
+        <v>9.448399999999999</v>
       </c>
       <c r="G47">
         <v>0.262</v>
@@ -5129,28 +5129,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M47">
-        <v>0.4649229</v>
+        <v>0.47525452</v>
       </c>
       <c r="N47">
-        <v>7.895077099999999</v>
+        <v>7.884745479999999</v>
       </c>
       <c r="O47">
-        <v>2.763276985</v>
+        <v>2.759660918</v>
       </c>
       <c r="P47">
-        <v>5.131800114999999</v>
+        <v>5.125084562</v>
       </c>
       <c r="Q47">
-        <v>6.771800115</v>
+        <v>6.765084562</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2728297845186374</v>
+        <v>0.276073423598473</v>
       </c>
       <c r="T47">
-        <v>1.115481828459408</v>
+        <v>1.131419034493008</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>17.98147606839758</v>
+        <v>17.59057441473676</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1641193487431754</v>
+        <v>0.1634695660011002</v>
       </c>
       <c r="C48">
-        <v>17.78151868500547</v>
+        <v>17.72503814435862</v>
       </c>
       <c r="D48">
-        <v>26.96791868500547</v>
+        <v>27.11683814435862</v>
       </c>
       <c r="E48">
-        <v>-2.6516</v>
+        <v>-2.446199999999999</v>
       </c>
       <c r="F48">
-        <v>9.448399999999999</v>
+        <v>9.6538</v>
       </c>
       <c r="G48">
         <v>0.262</v>
@@ -5211,28 +5211,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M48">
-        <v>0.47525452</v>
+        <v>0.48558614</v>
       </c>
       <c r="N48">
-        <v>7.884745479999999</v>
+        <v>7.87441386</v>
       </c>
       <c r="O48">
-        <v>2.759660918</v>
+        <v>2.756044851</v>
       </c>
       <c r="P48">
-        <v>5.125084562</v>
+        <v>5.118369009</v>
       </c>
       <c r="Q48">
-        <v>6.765084562</v>
+        <v>6.758369009000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.276073423598473</v>
+        <v>0.2794394641530192</v>
       </c>
       <c r="T48">
-        <v>1.131419034493008</v>
+        <v>1.147957644527875</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>17.59057441473676</v>
+        <v>17.21630687399768</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1634695660011002</v>
+        <v>0.1628197832590249</v>
       </c>
       <c r="C49">
-        <v>17.72503814435862</v>
+        <v>17.67021143167065</v>
       </c>
       <c r="D49">
-        <v>27.11683814435862</v>
+        <v>27.26741143167065</v>
       </c>
       <c r="E49">
-        <v>-2.446199999999999</v>
+        <v>-2.2408</v>
       </c>
       <c r="F49">
-        <v>9.6538</v>
+        <v>9.8592</v>
       </c>
       <c r="G49">
         <v>0.262</v>
@@ -5293,28 +5293,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M49">
-        <v>0.48558614</v>
+        <v>0.4959177599999999</v>
       </c>
       <c r="N49">
-        <v>7.87441386</v>
+        <v>7.864082239999999</v>
       </c>
       <c r="O49">
-        <v>2.756044851</v>
+        <v>2.752428784</v>
       </c>
       <c r="P49">
-        <v>5.118369009</v>
+        <v>5.111653455999999</v>
       </c>
       <c r="Q49">
-        <v>6.758369009000001</v>
+        <v>6.751653456</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2794394641530192</v>
+        <v>0.2829349678058172</v>
       </c>
       <c r="T49">
-        <v>1.147957644527875</v>
+        <v>1.165132354948699</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>17.21630687399768</v>
+        <v>16.85763381412273</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1628197832590249</v>
+        <v>0.1621700005169497</v>
       </c>
       <c r="C50">
-        <v>17.67021143167065</v>
+        <v>17.61706625070182</v>
       </c>
       <c r="D50">
-        <v>27.26741143167065</v>
+        <v>27.41966625070182</v>
       </c>
       <c r="E50">
-        <v>-2.2408</v>
+        <v>-2.035400000000001</v>
       </c>
       <c r="F50">
-        <v>9.8592</v>
+        <v>10.0646</v>
       </c>
       <c r="G50">
         <v>0.262</v>
@@ -5375,28 +5375,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M50">
-        <v>0.4959177599999999</v>
+        <v>0.5062493799999999</v>
       </c>
       <c r="N50">
-        <v>7.864082239999999</v>
+        <v>7.85375062</v>
       </c>
       <c r="O50">
-        <v>2.752428784</v>
+        <v>2.748812717</v>
       </c>
       <c r="P50">
-        <v>5.111653455999999</v>
+        <v>5.104937903</v>
       </c>
       <c r="Q50">
-        <v>6.751653456</v>
+        <v>6.744937903</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2829349678058172</v>
+        <v>0.2865675500332347</v>
       </c>
       <c r="T50">
-        <v>1.165132354948699</v>
+        <v>1.182980583425241</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>16.85763381412273</v>
+        <v>16.51360047097737</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1621700005169497</v>
+        <v>0.1615202177748745</v>
       </c>
       <c r="C51">
-        <v>17.61706625070182</v>
+        <v>17.56563092745199</v>
       </c>
       <c r="D51">
-        <v>27.41966625070182</v>
+        <v>27.57363092745199</v>
       </c>
       <c r="E51">
-        <v>-2.035400000000001</v>
+        <v>-1.83</v>
       </c>
       <c r="F51">
-        <v>10.0646</v>
+        <v>10.27</v>
       </c>
       <c r="G51">
         <v>0.262</v>
@@ -5457,28 +5457,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M51">
-        <v>0.5062493799999999</v>
+        <v>0.516581</v>
       </c>
       <c r="N51">
-        <v>7.85375062</v>
+        <v>7.843418999999999</v>
       </c>
       <c r="O51">
-        <v>2.748812717</v>
+        <v>2.74519665</v>
       </c>
       <c r="P51">
-        <v>5.104937903</v>
+        <v>5.098222349999999</v>
       </c>
       <c r="Q51">
-        <v>6.744937903</v>
+        <v>6.73822235</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2865675500332347</v>
+        <v>0.290345435549749</v>
       </c>
       <c r="T51">
-        <v>1.182980583425241</v>
+        <v>1.201542741040846</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>16.51360047097737</v>
+        <v>16.18332846155782</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1615202177748745</v>
+        <v>0.1608704350327993</v>
       </c>
       <c r="C52">
-        <v>17.56563092745199</v>
+        <v>17.51593442772904</v>
       </c>
       <c r="D52">
-        <v>27.57363092745199</v>
+        <v>27.72933442772904</v>
       </c>
       <c r="E52">
-        <v>-1.83</v>
+        <v>-1.624599999999999</v>
       </c>
       <c r="F52">
-        <v>10.27</v>
+        <v>10.4754</v>
       </c>
       <c r="G52">
         <v>0.262</v>
@@ -5539,28 +5539,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M52">
-        <v>0.516581</v>
+        <v>0.5269126200000001</v>
       </c>
       <c r="N52">
-        <v>7.843418999999999</v>
+        <v>7.833087379999999</v>
       </c>
       <c r="O52">
-        <v>2.74519665</v>
+        <v>2.741580583</v>
       </c>
       <c r="P52">
-        <v>5.098222349999999</v>
+        <v>5.091506796999999</v>
       </c>
       <c r="Q52">
-        <v>6.73822235</v>
+        <v>6.731506797</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.290345435549749</v>
+        <v>0.2942775204751005</v>
       </c>
       <c r="T52">
-        <v>1.201542741040846</v>
+        <v>1.220862537742801</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>16.18332846155782</v>
+        <v>15.86600829564492</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1608704350327993</v>
+        <v>0.160220652290724</v>
       </c>
       <c r="C53">
-        <v>17.51593442772904</v>
+        <v>17.46800637531582</v>
       </c>
       <c r="D53">
-        <v>27.72933442772904</v>
+        <v>27.88680637531582</v>
       </c>
       <c r="E53">
-        <v>-1.624599999999999</v>
+        <v>-1.4192</v>
       </c>
       <c r="F53">
-        <v>10.4754</v>
+        <v>10.6808</v>
       </c>
       <c r="G53">
         <v>0.262</v>
@@ -5621,28 +5621,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M53">
-        <v>0.5269126200000001</v>
+        <v>0.5372442399999999</v>
       </c>
       <c r="N53">
-        <v>7.833087379999999</v>
+        <v>7.82275576</v>
       </c>
       <c r="O53">
-        <v>2.741580583</v>
+        <v>2.737964516</v>
       </c>
       <c r="P53">
-        <v>5.091506796999999</v>
+        <v>5.084791244</v>
       </c>
       <c r="Q53">
-        <v>6.731506797</v>
+        <v>6.724791244</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2942775204751005</v>
+        <v>0.2983734422723417</v>
       </c>
       <c r="T53">
-        <v>1.220862537742801</v>
+        <v>1.240987325974005</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>15.86600829564492</v>
+        <v>15.5608927514979</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.160220652290724</v>
+        <v>0.1595708695486488</v>
       </c>
       <c r="C54">
-        <v>17.46800637531582</v>
+        <v>17.42187707075976</v>
       </c>
       <c r="D54">
-        <v>27.88680637531582</v>
+        <v>28.04607707075975</v>
       </c>
       <c r="E54">
-        <v>-1.4192</v>
+        <v>-1.213799999999999</v>
       </c>
       <c r="F54">
-        <v>10.6808</v>
+        <v>10.8862</v>
       </c>
       <c r="G54">
         <v>0.262</v>
@@ -5703,28 +5703,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M54">
-        <v>0.5372442399999999</v>
+        <v>0.54757586</v>
       </c>
       <c r="N54">
-        <v>7.82275576</v>
+        <v>7.812424139999999</v>
       </c>
       <c r="O54">
-        <v>2.737964516</v>
+        <v>2.734348449</v>
       </c>
       <c r="P54">
-        <v>5.084791244</v>
+        <v>5.078075691</v>
       </c>
       <c r="Q54">
-        <v>6.724791244</v>
+        <v>6.718075691</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2983734422723417</v>
+        <v>0.3026436586141464</v>
       </c>
       <c r="T54">
-        <v>1.240987325974005</v>
+        <v>1.261968488172494</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>15.5608927514979</v>
+        <v>15.26729100146964</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1595708695486488</v>
+        <v>0.1589210868065736</v>
       </c>
       <c r="C55">
-        <v>17.42187707075976</v>
+        <v>17.37757751080991</v>
       </c>
       <c r="D55">
-        <v>28.04607707075975</v>
+        <v>28.20717751080991</v>
       </c>
       <c r="E55">
-        <v>-1.213799999999999</v>
+        <v>-1.0084</v>
       </c>
       <c r="F55">
-        <v>10.8862</v>
+        <v>11.0916</v>
       </c>
       <c r="G55">
         <v>0.262</v>
@@ -5785,28 +5785,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M55">
-        <v>0.54757586</v>
+        <v>0.55790748</v>
       </c>
       <c r="N55">
-        <v>7.812424139999999</v>
+        <v>7.80209252</v>
       </c>
       <c r="O55">
-        <v>2.734348449</v>
+        <v>2.730732382</v>
       </c>
       <c r="P55">
-        <v>5.078075691</v>
+        <v>5.071360137999999</v>
       </c>
       <c r="Q55">
-        <v>6.718075691</v>
+        <v>6.711360138</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3026436586141464</v>
+        <v>0.3070995365360296</v>
       </c>
       <c r="T55">
-        <v>1.261968488172494</v>
+        <v>1.283861874814395</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>15.26729100146964</v>
+        <v>14.98456339033131</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1589210868065736</v>
+        <v>0.1582713040644984</v>
       </c>
       <c r="C56">
-        <v>17.37757751080991</v>
+        <v>17.33513940852798</v>
       </c>
       <c r="D56">
-        <v>28.20717751080991</v>
+        <v>28.37013940852798</v>
       </c>
       <c r="E56">
-        <v>-1.0084</v>
+        <v>-0.802999999999999</v>
       </c>
       <c r="F56">
-        <v>11.0916</v>
+        <v>11.297</v>
       </c>
       <c r="G56">
         <v>0.262</v>
@@ -5867,28 +5867,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M56">
-        <v>0.55790748</v>
+        <v>0.5682391</v>
       </c>
       <c r="N56">
-        <v>7.80209252</v>
+        <v>7.7917609</v>
       </c>
       <c r="O56">
-        <v>2.730732382</v>
+        <v>2.727116315</v>
       </c>
       <c r="P56">
-        <v>5.071360137999999</v>
+        <v>5.064644585</v>
       </c>
       <c r="Q56">
-        <v>6.711360138</v>
+        <v>6.704644585</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3070995365360296</v>
+        <v>0.3117534534766631</v>
       </c>
       <c r="T56">
-        <v>1.283861874814395</v>
+        <v>1.306728300862603</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>14.98456339033131</v>
+        <v>14.71211678323438</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1582713040644984</v>
+        <v>0.1576215213224231</v>
       </c>
       <c r="C57">
-        <v>17.33513940852798</v>
+        <v>17.2945952141003</v>
       </c>
       <c r="D57">
-        <v>28.37013940852798</v>
+        <v>28.5349952141003</v>
       </c>
       <c r="E57">
-        <v>-0.802999999999999</v>
+        <v>-0.5975999999999999</v>
       </c>
       <c r="F57">
-        <v>11.297</v>
+        <v>11.5024</v>
       </c>
       <c r="G57">
         <v>0.262</v>
@@ -5949,28 +5949,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M57">
-        <v>0.5682391</v>
+        <v>0.57857072</v>
       </c>
       <c r="N57">
-        <v>7.7917609</v>
+        <v>7.781429279999999</v>
       </c>
       <c r="O57">
-        <v>2.727116315</v>
+        <v>2.723500248</v>
       </c>
       <c r="P57">
-        <v>5.064644585</v>
+        <v>5.057929032</v>
       </c>
       <c r="Q57">
-        <v>6.704644585</v>
+        <v>6.697929032</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3117534534766631</v>
+        <v>0.3166189120964162</v>
       </c>
       <c r="T57">
-        <v>1.306728300862603</v>
+        <v>1.330634109913003</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>14.71211678323438</v>
+        <v>14.4494004121052</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1576215213224231</v>
+        <v>0.1569717385803479</v>
       </c>
       <c r="C58">
-        <v>17.2945952141003</v>
+        <v>17.25597813637978</v>
       </c>
       <c r="D58">
-        <v>28.5349952141003</v>
+        <v>28.70177813637978</v>
       </c>
       <c r="E58">
-        <v>-0.5975999999999999</v>
+        <v>-0.392199999999999</v>
       </c>
       <c r="F58">
-        <v>11.5024</v>
+        <v>11.7078</v>
       </c>
       <c r="G58">
         <v>0.262</v>
@@ -6031,28 +6031,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M58">
-        <v>0.57857072</v>
+        <v>0.58890234</v>
       </c>
       <c r="N58">
-        <v>7.781429279999999</v>
+        <v>7.77109766</v>
       </c>
       <c r="O58">
-        <v>2.723500248</v>
+        <v>2.719884181</v>
       </c>
       <c r="P58">
-        <v>5.057929032</v>
+        <v>5.051213478999999</v>
       </c>
       <c r="Q58">
-        <v>6.697929032</v>
+        <v>6.691213479</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3166189120964162</v>
+        <v>0.3217106711170882</v>
       </c>
       <c r="T58">
-        <v>1.330634109913003</v>
+        <v>1.35565181705877</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>14.4494004121052</v>
+        <v>14.19590215926125</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1569717385803479</v>
+        <v>0.1563219558382727</v>
       </c>
       <c r="C59">
-        <v>17.25597813637978</v>
+        <v>17.21932216518779</v>
       </c>
       <c r="D59">
-        <v>28.70177813637978</v>
+        <v>28.87052216518779</v>
       </c>
       <c r="E59">
-        <v>-0.392199999999999</v>
+        <v>-0.1867999999999981</v>
       </c>
       <c r="F59">
-        <v>11.7078</v>
+        <v>11.9132</v>
       </c>
       <c r="G59">
         <v>0.262</v>
@@ -6113,28 +6113,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M59">
-        <v>0.58890234</v>
+        <v>0.5992339600000001</v>
       </c>
       <c r="N59">
-        <v>7.77109766</v>
+        <v>7.760766039999999</v>
       </c>
       <c r="O59">
-        <v>2.719884181</v>
+        <v>2.716268114</v>
       </c>
       <c r="P59">
-        <v>5.051213478999999</v>
+        <v>5.044497926</v>
       </c>
       <c r="Q59">
-        <v>6.691213479</v>
+        <v>6.684497926000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3217106711170882</v>
+        <v>0.3270448948530303</v>
       </c>
       <c r="T59">
-        <v>1.35565181705877</v>
+        <v>1.38186084359243</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>14.19590215926125</v>
+        <v>13.95114522548088</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1563219558382727</v>
+        <v>0.1556721730961975</v>
       </c>
       <c r="C60">
-        <v>17.2193221651878</v>
+        <v>17.18466209440732</v>
       </c>
       <c r="D60">
-        <v>28.87052216518779</v>
+        <v>29.04126209440731</v>
       </c>
       <c r="E60">
-        <v>-0.1868000000000016</v>
+        <v>0.01859999999999928</v>
       </c>
       <c r="F60">
-        <v>11.9132</v>
+        <v>12.1186</v>
       </c>
       <c r="G60">
         <v>0.262</v>
@@ -6195,28 +6195,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M60">
-        <v>0.5992339599999998</v>
+        <v>0.6095655799999999</v>
       </c>
       <c r="N60">
-        <v>7.76076604</v>
+        <v>7.750434419999999</v>
       </c>
       <c r="O60">
-        <v>2.716268114</v>
+        <v>2.712652047</v>
       </c>
       <c r="P60">
-        <v>5.044497926</v>
+        <v>5.037782373</v>
       </c>
       <c r="Q60">
-        <v>6.684497926000001</v>
+        <v>6.677782373</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3270448948530302</v>
+        <v>0.3326393246248718</v>
       </c>
       <c r="T60">
-        <v>1.38186084359243</v>
+        <v>1.409348359225293</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>13.95114522548088</v>
+        <v>13.71468513691341</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1556721730961975</v>
+        <v>0.1550223903541222</v>
       </c>
       <c r="C61">
-        <v>17.18466209440732</v>
+        <v>17.15203354590043</v>
       </c>
       <c r="D61">
-        <v>29.04126209440731</v>
+        <v>29.21403354590043</v>
       </c>
       <c r="E61">
-        <v>0.01859999999999928</v>
+        <v>0.2240000000000002</v>
       </c>
       <c r="F61">
-        <v>12.1186</v>
+        <v>12.324</v>
       </c>
       <c r="G61">
         <v>0.262</v>
@@ -6277,28 +6277,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M61">
-        <v>0.6095655799999999</v>
+        <v>0.6198971999999999</v>
       </c>
       <c r="N61">
-        <v>7.750434419999999</v>
+        <v>7.7401028</v>
       </c>
       <c r="O61">
-        <v>2.712652047</v>
+        <v>2.70903598</v>
       </c>
       <c r="P61">
-        <v>5.037782373</v>
+        <v>5.031066819999999</v>
       </c>
       <c r="Q61">
-        <v>6.677782373</v>
+        <v>6.67106682</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3326393246248718</v>
+        <v>0.3385134758853056</v>
       </c>
       <c r="T61">
-        <v>1.409348359225293</v>
+        <v>1.4382102506398</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>13.71468513691341</v>
+        <v>13.48610705129818</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1550223903541222</v>
+        <v>0.154372607612047</v>
       </c>
       <c r="C62">
-        <v>17.15203354590043</v>
+        <v>17.12147299428471</v>
       </c>
       <c r="D62">
-        <v>29.21403354590043</v>
+        <v>29.3888729942847</v>
       </c>
       <c r="E62">
-        <v>0.2240000000000002</v>
+        <v>0.4293999999999993</v>
       </c>
       <c r="F62">
-        <v>12.324</v>
+        <v>12.5294</v>
       </c>
       <c r="G62">
         <v>0.262</v>
@@ -6359,28 +6359,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M62">
-        <v>0.6198971999999999</v>
+        <v>0.6302288199999999</v>
       </c>
       <c r="N62">
-        <v>7.7401028</v>
+        <v>7.729771179999999</v>
       </c>
       <c r="O62">
-        <v>2.70903598</v>
+        <v>2.705419913</v>
       </c>
       <c r="P62">
-        <v>5.031066819999999</v>
+        <v>5.024351267</v>
       </c>
       <c r="Q62">
-        <v>6.67106682</v>
+        <v>6.664351267000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3385134758853056</v>
+        <v>0.3446888656719154</v>
       </c>
       <c r="T62">
-        <v>1.4382102506398</v>
+        <v>1.468552239049923</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>13.48610705129818</v>
+        <v>13.26502332914575</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.154372607612047</v>
+        <v>0.1537228248699718</v>
       </c>
       <c r="C63">
-        <v>17.12147299428471</v>
+        <v>17.09301779260456</v>
       </c>
       <c r="D63">
-        <v>29.3888729942847</v>
+        <v>29.56581779260456</v>
       </c>
       <c r="E63">
-        <v>0.4293999999999993</v>
+        <v>0.6348000000000003</v>
       </c>
       <c r="F63">
-        <v>12.5294</v>
+        <v>12.7348</v>
       </c>
       <c r="G63">
         <v>0.262</v>
@@ -6441,28 +6441,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M63">
-        <v>0.6302288199999999</v>
+        <v>0.64056044</v>
       </c>
       <c r="N63">
-        <v>7.729771179999999</v>
+        <v>7.71943956</v>
       </c>
       <c r="O63">
-        <v>2.705419913</v>
+        <v>2.701803846</v>
       </c>
       <c r="P63">
-        <v>5.024351267</v>
+        <v>5.017635714</v>
       </c>
       <c r="Q63">
-        <v>6.664351267000001</v>
+        <v>6.657635714</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3446888656719154</v>
+        <v>0.35118927597361</v>
       </c>
       <c r="T63">
-        <v>1.468552239049923</v>
+        <v>1.500491174218473</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>13.26502332914575</v>
+        <v>13.05107133996598</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1537228248699718</v>
+        <v>0.1536872921278966</v>
       </c>
       <c r="C64">
-        <v>17.09301779260456</v>
+        <v>16.89735531179841</v>
       </c>
       <c r="D64">
-        <v>29.56581779260456</v>
+        <v>29.57555531179841</v>
       </c>
       <c r="E64">
-        <v>0.6348000000000003</v>
+        <v>0.8401999999999994</v>
       </c>
       <c r="F64">
-        <v>12.7348</v>
+        <v>12.9402</v>
       </c>
       <c r="G64">
         <v>0.262</v>
@@ -6523,45 +6523,45 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M64">
-        <v>0.64056044</v>
+        <v>0.67030236</v>
       </c>
       <c r="N64">
-        <v>7.71943956</v>
+        <v>7.689697639999999</v>
       </c>
       <c r="O64">
-        <v>2.701803846</v>
+        <v>2.691394174</v>
       </c>
       <c r="P64">
-        <v>5.017635714</v>
+        <v>4.998303465999999</v>
       </c>
       <c r="Q64">
-        <v>6.657635714</v>
+        <v>6.638303466</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.35118927597361</v>
+        <v>0.3580410598051258</v>
       </c>
       <c r="T64">
-        <v>1.500491174218473</v>
+        <v>1.534156538315052</v>
       </c>
       <c r="U64">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y64">
-        <v>13.05107133996598</v>
+        <v>12.47198353889131</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1536872921278966</v>
+        <v>0.1530472593858213</v>
       </c>
       <c r="C65">
-        <v>16.89735531179841</v>
+        <v>16.86845701331519</v>
       </c>
       <c r="D65">
-        <v>29.57555531179841</v>
+        <v>29.75205701331518</v>
       </c>
       <c r="E65">
-        <v>0.8401999999999994</v>
+        <v>1.0456</v>
       </c>
       <c r="F65">
-        <v>12.9402</v>
+        <v>13.1456</v>
       </c>
       <c r="G65">
         <v>0.262</v>
@@ -6605,28 +6605,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M65">
-        <v>0.67030236</v>
+        <v>0.68094208</v>
       </c>
       <c r="N65">
-        <v>7.689697639999999</v>
+        <v>7.679057919999999</v>
       </c>
       <c r="O65">
-        <v>2.691394174</v>
+        <v>2.687670272</v>
       </c>
       <c r="P65">
-        <v>4.998303465999999</v>
+        <v>4.991387648</v>
       </c>
       <c r="Q65">
-        <v>6.638303466</v>
+        <v>6.631387648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3580410598051258</v>
+        <v>0.3652734982939482</v>
       </c>
       <c r="T65">
-        <v>1.534156538315052</v>
+        <v>1.569692200416997</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>12.47198353889131</v>
+        <v>12.27710879609614</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1530472593858213</v>
+        <v>0.1524072266437461</v>
       </c>
       <c r="C66">
-        <v>16.86845701331519</v>
+        <v>16.84167802459282</v>
       </c>
       <c r="D66">
-        <v>29.75205701331518</v>
+        <v>29.93067802459282</v>
       </c>
       <c r="E66">
-        <v>1.0456</v>
+        <v>1.250999999999999</v>
       </c>
       <c r="F66">
-        <v>13.1456</v>
+        <v>13.351</v>
       </c>
       <c r="G66">
         <v>0.262</v>
@@ -6687,28 +6687,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M66">
-        <v>0.68094208</v>
+        <v>0.6915817999999999</v>
       </c>
       <c r="N66">
-        <v>7.679057919999999</v>
+        <v>7.6684182</v>
       </c>
       <c r="O66">
-        <v>2.687670272</v>
+        <v>2.68394637</v>
       </c>
       <c r="P66">
-        <v>4.991387648</v>
+        <v>4.98447183</v>
       </c>
       <c r="Q66">
-        <v>6.631387648</v>
+        <v>6.624471830000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3652734982939482</v>
+        <v>0.3729192189821318</v>
       </c>
       <c r="T66">
-        <v>1.569692200416997</v>
+        <v>1.607258471781911</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>12.27710879609614</v>
+        <v>12.08823019923312</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1524072266437461</v>
+        <v>0.1517671939016709</v>
       </c>
       <c r="C67">
-        <v>16.84167802459282</v>
+        <v>16.81705674697767</v>
       </c>
       <c r="D67">
-        <v>29.93067802459282</v>
+        <v>30.11145674697767</v>
       </c>
       <c r="E67">
-        <v>1.250999999999999</v>
+        <v>1.4564</v>
       </c>
       <c r="F67">
-        <v>13.351</v>
+        <v>13.5564</v>
       </c>
       <c r="G67">
         <v>0.262</v>
@@ -6769,28 +6769,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M67">
-        <v>0.6915817999999999</v>
+        <v>0.7022215199999999</v>
       </c>
       <c r="N67">
-        <v>7.6684182</v>
+        <v>7.657778479999999</v>
       </c>
       <c r="O67">
-        <v>2.68394637</v>
+        <v>2.680222468</v>
       </c>
       <c r="P67">
-        <v>4.98447183</v>
+        <v>4.977556011999999</v>
       </c>
       <c r="Q67">
-        <v>6.624471830000001</v>
+        <v>6.617556012</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3729192189821318</v>
+        <v>0.3810146879460908</v>
       </c>
       <c r="T67">
-        <v>1.607258471781911</v>
+        <v>1.647034523815348</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>12.08823019923312</v>
+        <v>11.90507519621444</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1517671939016709</v>
+        <v>0.1511271611595957</v>
       </c>
       <c r="C68">
-        <v>16.81705674697767</v>
+        <v>16.79463251521702</v>
       </c>
       <c r="D68">
-        <v>30.11145674697767</v>
+        <v>30.29443251521703</v>
       </c>
       <c r="E68">
-        <v>1.4564</v>
+        <v>1.661800000000001</v>
       </c>
       <c r="F68">
-        <v>13.5564</v>
+        <v>13.7618</v>
       </c>
       <c r="G68">
         <v>0.262</v>
@@ -6851,28 +6851,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M68">
-        <v>0.7022215199999999</v>
+        <v>0.7128612400000001</v>
       </c>
       <c r="N68">
-        <v>7.657778479999999</v>
+        <v>7.647138759999999</v>
       </c>
       <c r="O68">
-        <v>2.680222468</v>
+        <v>2.676498565999999</v>
       </c>
       <c r="P68">
-        <v>4.977556011999999</v>
+        <v>4.970640194</v>
       </c>
       <c r="Q68">
-        <v>6.617556012</v>
+        <v>6.610640194</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3810146879460908</v>
+        <v>0.3896007913927142</v>
       </c>
       <c r="T68">
-        <v>1.647034523815348</v>
+        <v>1.689221245668995</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>11.90507519621444</v>
+        <v>11.7273875067187</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1511271611595957</v>
+        <v>0.1504871284175204</v>
       </c>
       <c r="C69">
-        <v>16.79463251521702</v>
+        <v>16.77444562599218</v>
       </c>
       <c r="D69">
-        <v>30.29443251521703</v>
+        <v>30.47964562599218</v>
       </c>
       <c r="E69">
-        <v>1.661800000000001</v>
+        <v>1.8672</v>
       </c>
       <c r="F69">
-        <v>13.7618</v>
+        <v>13.9672</v>
       </c>
       <c r="G69">
         <v>0.262</v>
@@ -6933,28 +6933,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M69">
-        <v>0.7128612400000001</v>
+        <v>0.72350096</v>
       </c>
       <c r="N69">
-        <v>7.647138759999999</v>
+        <v>7.636499039999999</v>
       </c>
       <c r="O69">
-        <v>2.676498565999999</v>
+        <v>2.672774664</v>
       </c>
       <c r="P69">
-        <v>4.970640194</v>
+        <v>4.963724376</v>
       </c>
       <c r="Q69">
-        <v>6.610640194</v>
+        <v>6.603724376000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3896007913927142</v>
+        <v>0.3987235263047514</v>
       </c>
       <c r="T69">
-        <v>1.689221245668995</v>
+        <v>1.734044637638494</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>11.7273875067187</v>
+        <v>11.55492592573754</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1504871284175204</v>
+        <v>0.1498470956754452</v>
       </c>
       <c r="C70">
-        <v>16.77444562599218</v>
+        <v>16.75653736750446</v>
       </c>
       <c r="D70">
-        <v>30.47964562599218</v>
+        <v>30.66713736750446</v>
       </c>
       <c r="E70">
-        <v>1.8672</v>
+        <v>2.072600000000001</v>
       </c>
       <c r="F70">
-        <v>13.9672</v>
+        <v>14.1726</v>
       </c>
       <c r="G70">
         <v>0.262</v>
@@ -7015,28 +7015,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M70">
-        <v>0.72350096</v>
+        <v>0.73414068</v>
       </c>
       <c r="N70">
-        <v>7.636499039999999</v>
+        <v>7.625859319999999</v>
       </c>
       <c r="O70">
-        <v>2.672774664</v>
+        <v>2.669050761999999</v>
       </c>
       <c r="P70">
-        <v>4.963724376</v>
+        <v>4.956808558</v>
       </c>
       <c r="Q70">
-        <v>6.603724376000001</v>
+        <v>6.596808558</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3987235263047514</v>
+        <v>0.4084348247595007</v>
       </c>
       <c r="T70">
-        <v>1.734044637638494</v>
+        <v>1.78175986134796</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>11.55492592573754</v>
+        <v>11.38746323116163</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1498470956754452</v>
+        <v>0.14920706293337</v>
       </c>
       <c r="C71">
-        <v>16.75653736750446</v>
+        <v>16.74095005016008</v>
       </c>
       <c r="D71">
-        <v>30.66713736750446</v>
+        <v>30.85695005016008</v>
       </c>
       <c r="E71">
-        <v>2.072600000000001</v>
+        <v>2.278</v>
       </c>
       <c r="F71">
-        <v>14.1726</v>
+        <v>14.378</v>
       </c>
       <c r="G71">
         <v>0.262</v>
@@ -7097,28 +7097,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M71">
-        <v>0.73414068</v>
+        <v>0.7447804</v>
       </c>
       <c r="N71">
-        <v>7.625859319999999</v>
+        <v>7.6152196</v>
       </c>
       <c r="O71">
-        <v>2.669050761999999</v>
+        <v>2.66532686</v>
       </c>
       <c r="P71">
-        <v>4.956808558</v>
+        <v>4.94989274</v>
       </c>
       <c r="Q71">
-        <v>6.596808558</v>
+        <v>6.589892740000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4084348247595007</v>
+        <v>0.4187935431112333</v>
       </c>
       <c r="T71">
-        <v>1.78175986134796</v>
+        <v>1.832656099971391</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>11.38746323116163</v>
+        <v>11.22478518500218</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.14920706293337</v>
+        <v>0.1485670301912947</v>
       </c>
       <c r="C72">
-        <v>16.74095005016008</v>
+        <v>16.72772703840155</v>
       </c>
       <c r="D72">
-        <v>30.85695005016008</v>
+        <v>31.04912703840155</v>
       </c>
       <c r="E72">
-        <v>2.278</v>
+        <v>2.483400000000001</v>
       </c>
       <c r="F72">
-        <v>14.378</v>
+        <v>14.5834</v>
       </c>
       <c r="G72">
         <v>0.262</v>
@@ -7179,28 +7179,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M72">
-        <v>0.7447804</v>
+        <v>0.75542012</v>
       </c>
       <c r="N72">
-        <v>7.6152196</v>
+        <v>7.604579879999999</v>
       </c>
       <c r="O72">
-        <v>2.66532686</v>
+        <v>2.661602958</v>
       </c>
       <c r="P72">
-        <v>4.94989274</v>
+        <v>4.942976922</v>
       </c>
       <c r="Q72">
-        <v>6.589892740000001</v>
+        <v>6.582976922</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4187935431112333</v>
+        <v>0.429866655832051</v>
       </c>
       <c r="T72">
-        <v>1.832656099971391</v>
+        <v>1.887062424017128</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>11.22478518500218</v>
+        <v>11.06668961901624</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1485670301912948</v>
+        <v>0.1479269974492195</v>
       </c>
       <c r="C73">
-        <v>16.72772703840155</v>
+        <v>16.71691278373604</v>
       </c>
       <c r="D73">
-        <v>31.04912703840154</v>
+        <v>31.24371278373604</v>
       </c>
       <c r="E73">
-        <v>2.4834</v>
+        <v>2.688799999999999</v>
       </c>
       <c r="F73">
-        <v>14.5834</v>
+        <v>14.7888</v>
       </c>
       <c r="G73">
         <v>0.262</v>
@@ -7261,28 +7261,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M73">
-        <v>0.7554201199999999</v>
+        <v>0.7660598399999999</v>
       </c>
       <c r="N73">
-        <v>7.604579879999999</v>
+        <v>7.59394016</v>
       </c>
       <c r="O73">
-        <v>2.661602958</v>
+        <v>2.657879056</v>
       </c>
       <c r="P73">
-        <v>4.942976922</v>
+        <v>4.936061104</v>
       </c>
       <c r="Q73">
-        <v>6.582976922</v>
+        <v>6.576061104000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4298666558320509</v>
+        <v>0.441730705175784</v>
       </c>
       <c r="T73">
-        <v>1.887062424017128</v>
+        <v>1.945354914066131</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>11.06668961901624</v>
+        <v>10.9129855965299</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1479269974492195</v>
+        <v>0.1472869647071443</v>
       </c>
       <c r="C74">
-        <v>16.71691278373604</v>
+        <v>16.70855285901359</v>
       </c>
       <c r="D74">
-        <v>31.24371278373604</v>
+        <v>31.44075285901359</v>
       </c>
       <c r="E74">
-        <v>2.688799999999999</v>
+        <v>2.8942</v>
       </c>
       <c r="F74">
-        <v>14.7888</v>
+        <v>14.9942</v>
       </c>
       <c r="G74">
         <v>0.262</v>
@@ -7343,28 +7343,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M74">
-        <v>0.7660598399999999</v>
+        <v>0.77669956</v>
       </c>
       <c r="N74">
-        <v>7.59394016</v>
+        <v>7.583300439999999</v>
       </c>
       <c r="O74">
-        <v>2.657879056</v>
+        <v>2.654155154</v>
       </c>
       <c r="P74">
-        <v>4.936061104</v>
+        <v>4.929145286</v>
       </c>
       <c r="Q74">
-        <v>6.576061104000001</v>
+        <v>6.569145286</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.441730705175784</v>
+        <v>0.4544735729894233</v>
       </c>
       <c r="T74">
-        <v>1.945354914066131</v>
+        <v>2.007965366340986</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>10.9129855965299</v>
+        <v>10.76349264315278</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1472869647071443</v>
+        <v>0.1466469319650691</v>
       </c>
       <c r="C75">
-        <v>16.70855285901359</v>
+        <v>16.70269399401048</v>
       </c>
       <c r="D75">
-        <v>31.44075285901359</v>
+        <v>31.64029399401048</v>
       </c>
       <c r="E75">
-        <v>2.8942</v>
+        <v>3.099599999999999</v>
       </c>
       <c r="F75">
-        <v>14.9942</v>
+        <v>15.1996</v>
       </c>
       <c r="G75">
         <v>0.262</v>
@@ -7425,28 +7425,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M75">
-        <v>0.77669956</v>
+        <v>0.7873392799999999</v>
       </c>
       <c r="N75">
-        <v>7.583300439999999</v>
+        <v>7.57266072</v>
       </c>
       <c r="O75">
-        <v>2.654155154</v>
+        <v>2.650431252</v>
       </c>
       <c r="P75">
-        <v>4.929145286</v>
+        <v>4.922229468</v>
       </c>
       <c r="Q75">
-        <v>6.569145286</v>
+        <v>6.562229468000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4544735729894233</v>
+        <v>0.4681966614041118</v>
       </c>
       <c r="T75">
-        <v>2.007965366340986</v>
+        <v>2.07539200725237</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>10.76349264315278</v>
+        <v>10.61804003986693</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1466469319650691</v>
+        <v>0.1460068992229939</v>
       </c>
       <c r="C76">
-        <v>16.70269399401048</v>
+        <v>16.69938411237635</v>
       </c>
       <c r="D76">
-        <v>31.64029399401048</v>
+        <v>31.84238411237635</v>
       </c>
       <c r="E76">
-        <v>3.099599999999999</v>
+        <v>3.305</v>
       </c>
       <c r="F76">
-        <v>15.1996</v>
+        <v>15.405</v>
       </c>
       <c r="G76">
         <v>0.262</v>
@@ -7507,28 +7507,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M76">
-        <v>0.7873392799999999</v>
+        <v>0.797979</v>
       </c>
       <c r="N76">
-        <v>7.57266072</v>
+        <v>7.562021</v>
       </c>
       <c r="O76">
-        <v>2.650431252</v>
+        <v>2.64670735</v>
       </c>
       <c r="P76">
-        <v>4.922229468</v>
+        <v>4.91531365</v>
       </c>
       <c r="Q76">
-        <v>6.562229468000001</v>
+        <v>6.55531365</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4681966614041118</v>
+        <v>0.4830175968919754</v>
       </c>
       <c r="T76">
-        <v>2.07539200725237</v>
+        <v>2.148212779436664</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>10.61804003986693</v>
+        <v>10.4764661726687</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1460068992229939</v>
+        <v>0.1453668664809186</v>
       </c>
       <c r="C77">
-        <v>16.69938411237635</v>
+        <v>16.69867237000635</v>
       </c>
       <c r="D77">
-        <v>31.84238411237635</v>
+        <v>32.04707237000635</v>
       </c>
       <c r="E77">
-        <v>3.305</v>
+        <v>3.510400000000001</v>
       </c>
       <c r="F77">
-        <v>15.405</v>
+        <v>15.6104</v>
       </c>
       <c r="G77">
         <v>0.262</v>
@@ -7589,28 +7589,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M77">
-        <v>0.797979</v>
+        <v>0.80861872</v>
       </c>
       <c r="N77">
-        <v>7.562021</v>
+        <v>7.551381279999999</v>
       </c>
       <c r="O77">
-        <v>2.64670735</v>
+        <v>2.642983447999999</v>
       </c>
       <c r="P77">
-        <v>4.91531365</v>
+        <v>4.908397832</v>
       </c>
       <c r="Q77">
-        <v>6.55531365</v>
+        <v>6.548397832000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4830175968919754</v>
+        <v>0.499073610337161</v>
       </c>
       <c r="T77">
-        <v>2.148212779436664</v>
+        <v>2.227101949302982</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>10.4764661726687</v>
+        <v>10.33861793355464</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1453668664809186</v>
+        <v>0.1447268337388434</v>
       </c>
       <c r="C78">
-        <v>16.69867237000635</v>
+        <v>16.70060919490268</v>
       </c>
       <c r="D78">
-        <v>32.04707237000635</v>
+        <v>32.25440919490268</v>
       </c>
       <c r="E78">
-        <v>3.510400000000001</v>
+        <v>3.7158</v>
       </c>
       <c r="F78">
-        <v>15.6104</v>
+        <v>15.8158</v>
       </c>
       <c r="G78">
         <v>0.262</v>
@@ -7671,28 +7671,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M78">
-        <v>0.80861872</v>
+        <v>0.8192584399999999</v>
       </c>
       <c r="N78">
-        <v>7.551381279999999</v>
+        <v>7.54074156</v>
       </c>
       <c r="O78">
-        <v>2.642983447999999</v>
+        <v>2.639259546</v>
       </c>
       <c r="P78">
-        <v>4.908397832</v>
+        <v>4.901482014</v>
       </c>
       <c r="Q78">
-        <v>6.548397832000001</v>
+        <v>6.541482014000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.499073610337161</v>
+        <v>0.5165257988645365</v>
       </c>
       <c r="T78">
-        <v>2.227101949302982</v>
+        <v>2.312851046983762</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>10.33861793355464</v>
+        <v>10.2043501681838</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1447268337388434</v>
+        <v>0.1440868009967682</v>
       </c>
       <c r="C79">
-        <v>16.70060919490268</v>
+        <v>16.70524632859379</v>
       </c>
       <c r="D79">
-        <v>32.25440919490268</v>
+        <v>32.46444632859379</v>
       </c>
       <c r="E79">
-        <v>3.7158</v>
+        <v>3.921200000000001</v>
       </c>
       <c r="F79">
-        <v>15.8158</v>
+        <v>16.0212</v>
       </c>
       <c r="G79">
         <v>0.262</v>
@@ -7753,28 +7753,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M79">
-        <v>0.8192584399999999</v>
+        <v>0.8298981600000001</v>
       </c>
       <c r="N79">
-        <v>7.54074156</v>
+        <v>7.530101839999999</v>
       </c>
       <c r="O79">
-        <v>2.639259546</v>
+        <v>2.635535644</v>
       </c>
       <c r="P79">
-        <v>4.901482014</v>
+        <v>4.894566196</v>
       </c>
       <c r="Q79">
-        <v>6.541482014000001</v>
+        <v>6.534566196</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5165257988645365</v>
+        <v>0.5355645499853099</v>
       </c>
       <c r="T79">
-        <v>2.312851046983762</v>
+        <v>2.406395517180977</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>10.2043501681838</v>
+        <v>10.0735251660276</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1440868009967682</v>
+        <v>0.1434467682546929</v>
       </c>
       <c r="C80">
-        <v>16.70524632859379</v>
+        <v>16.71263686918237</v>
       </c>
       <c r="D80">
-        <v>32.46444632859379</v>
+        <v>32.67723686918237</v>
       </c>
       <c r="E80">
-        <v>3.921200000000001</v>
+        <v>4.126600000000002</v>
       </c>
       <c r="F80">
-        <v>16.0212</v>
+        <v>16.2266</v>
       </c>
       <c r="G80">
         <v>0.262</v>
@@ -7835,28 +7835,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M80">
-        <v>0.8298981600000001</v>
+        <v>0.8405378800000001</v>
       </c>
       <c r="N80">
-        <v>7.530101839999999</v>
+        <v>7.519462119999999</v>
       </c>
       <c r="O80">
-        <v>2.635535644</v>
+        <v>2.631811742</v>
       </c>
       <c r="P80">
-        <v>4.894566196</v>
+        <v>4.887650378</v>
       </c>
       <c r="Q80">
-        <v>6.534566196</v>
+        <v>6.527650378000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5355645499853099</v>
+        <v>0.5564165154985379</v>
       </c>
       <c r="T80">
-        <v>2.406395517180977</v>
+        <v>2.508848984539833</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.0735251660276</v>
+        <v>9.946012189242438</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1434467682546929</v>
+        <v>0.1428067355126177</v>
       </c>
       <c r="C81">
-        <v>16.71263686918237</v>
+        <v>16.72283531609748</v>
       </c>
       <c r="D81">
-        <v>32.67723686918237</v>
+        <v>32.89283531609748</v>
       </c>
       <c r="E81">
-        <v>4.126600000000002</v>
+        <v>4.331999999999999</v>
       </c>
       <c r="F81">
-        <v>16.2266</v>
+        <v>16.432</v>
       </c>
       <c r="G81">
         <v>0.262</v>
@@ -7917,28 +7917,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M81">
-        <v>0.8405378800000001</v>
+        <v>0.8511775999999999</v>
       </c>
       <c r="N81">
-        <v>7.519462119999999</v>
+        <v>7.5088224</v>
       </c>
       <c r="O81">
-        <v>2.631811742</v>
+        <v>2.62808784</v>
       </c>
       <c r="P81">
-        <v>4.887650378</v>
+        <v>4.88073456</v>
       </c>
       <c r="Q81">
-        <v>6.527650378000001</v>
+        <v>6.520734560000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5564165154985379</v>
+        <v>0.5793536775630886</v>
       </c>
       <c r="T81">
-        <v>2.508848984539833</v>
+        <v>2.621547798634573</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>9.946012189242438</v>
+        <v>9.821687036876911</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1428067355126177</v>
+        <v>0.1430617527705425</v>
       </c>
       <c r="C82">
-        <v>16.72283531609748</v>
+        <v>16.43119133602575</v>
       </c>
       <c r="D82">
-        <v>32.89283531609748</v>
+        <v>32.80659133602575</v>
       </c>
       <c r="E82">
-        <v>4.331999999999999</v>
+        <v>4.5374</v>
       </c>
       <c r="F82">
-        <v>16.432</v>
+        <v>16.6374</v>
       </c>
       <c r="G82">
         <v>0.262</v>
@@ -7999,45 +7999,45 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M82">
-        <v>0.8511775999999999</v>
+        <v>0.8901009</v>
       </c>
       <c r="N82">
-        <v>7.5088224</v>
+        <v>7.469899099999999</v>
       </c>
       <c r="O82">
-        <v>2.62808784</v>
+        <v>2.614464685</v>
       </c>
       <c r="P82">
-        <v>4.88073456</v>
+        <v>4.855434415</v>
       </c>
       <c r="Q82">
-        <v>6.520734560000001</v>
+        <v>6.495434415</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5793536775630886</v>
+        <v>0.6047052777396975</v>
       </c>
       <c r="T82">
-        <v>2.621547798634573</v>
+        <v>2.746109645791918</v>
       </c>
       <c r="U82">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>9.821687036876911</v>
+        <v>9.392193626587726</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1430617527705425</v>
+        <v>0.1424327700284673</v>
       </c>
       <c r="C83">
-        <v>16.43119133602575</v>
+        <v>16.43932945327724</v>
       </c>
       <c r="D83">
-        <v>32.80659133602575</v>
+        <v>33.02012945327724</v>
       </c>
       <c r="E83">
-        <v>4.5374</v>
+        <v>4.742800000000001</v>
       </c>
       <c r="F83">
-        <v>16.6374</v>
+        <v>16.8428</v>
       </c>
       <c r="G83">
         <v>0.262</v>
@@ -8081,28 +8081,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M83">
-        <v>0.8901009</v>
+        <v>0.9010898000000001</v>
       </c>
       <c r="N83">
-        <v>7.469899099999999</v>
+        <v>7.458910199999999</v>
       </c>
       <c r="O83">
-        <v>2.614464685</v>
+        <v>2.61061857</v>
       </c>
       <c r="P83">
-        <v>4.855434415</v>
+        <v>4.848291629999999</v>
       </c>
       <c r="Q83">
-        <v>6.495434415</v>
+        <v>6.48829163</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6047052777396975</v>
+        <v>0.6328737223803739</v>
       </c>
       <c r="T83">
-        <v>2.746109645791918</v>
+        <v>2.884511698188967</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>9.392193626587726</v>
+        <v>9.277654679922023</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1424327700284673</v>
+        <v>0.1418037872863921</v>
       </c>
       <c r="C84">
-        <v>16.43932945327724</v>
+        <v>16.45026562244569</v>
       </c>
       <c r="D84">
-        <v>33.02012945327724</v>
+        <v>33.23646562244569</v>
       </c>
       <c r="E84">
-        <v>4.742800000000001</v>
+        <v>4.948200000000002</v>
       </c>
       <c r="F84">
-        <v>16.8428</v>
+        <v>17.0482</v>
       </c>
       <c r="G84">
         <v>0.262</v>
@@ -8163,28 +8163,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M84">
-        <v>0.9010898000000001</v>
+        <v>0.9120787</v>
       </c>
       <c r="N84">
-        <v>7.458910199999999</v>
+        <v>7.447921299999999</v>
       </c>
       <c r="O84">
-        <v>2.61061857</v>
+        <v>2.606772454999999</v>
       </c>
       <c r="P84">
-        <v>4.848291629999999</v>
+        <v>4.841148844999999</v>
       </c>
       <c r="Q84">
-        <v>6.48829163</v>
+        <v>6.481148845</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6328737223803739</v>
+        <v>0.6643561016846594</v>
       </c>
       <c r="T84">
-        <v>2.884511698188967</v>
+        <v>3.03919634498567</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>9.277654679922023</v>
+        <v>9.165875707874768</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1418037872863921</v>
+        <v>0.1411748045443168</v>
       </c>
       <c r="C85">
-        <v>16.45026562244569</v>
+        <v>16.46405520174785</v>
       </c>
       <c r="D85">
-        <v>33.23646562244569</v>
+        <v>33.45565520174785</v>
       </c>
       <c r="E85">
-        <v>4.948200000000002</v>
+        <v>5.153600000000003</v>
       </c>
       <c r="F85">
-        <v>17.0482</v>
+        <v>17.2536</v>
       </c>
       <c r="G85">
         <v>0.262</v>
@@ -8245,28 +8245,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M85">
-        <v>0.9120787</v>
+        <v>0.9230676000000001</v>
       </c>
       <c r="N85">
-        <v>7.447921299999999</v>
+        <v>7.436932399999999</v>
       </c>
       <c r="O85">
-        <v>2.606772454999999</v>
+        <v>2.602926339999999</v>
       </c>
       <c r="P85">
-        <v>4.841148844999999</v>
+        <v>4.83400606</v>
       </c>
       <c r="Q85">
-        <v>6.481148845</v>
+        <v>6.474006060000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6643561016846594</v>
+        <v>0.6997737784019804</v>
       </c>
       <c r="T85">
-        <v>3.03919634498567</v>
+        <v>3.21321657263196</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>9.165875707874768</v>
+        <v>9.056758139923877</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1411748045443168</v>
+        <v>0.1405458218022416</v>
       </c>
       <c r="C86">
-        <v>16.46405520174785</v>
+        <v>16.480755019412</v>
       </c>
       <c r="D86">
-        <v>33.45565520174785</v>
+        <v>33.677755019412</v>
       </c>
       <c r="E86">
-        <v>5.153599999999999</v>
+        <v>5.359</v>
       </c>
       <c r="F86">
-        <v>17.2536</v>
+        <v>17.459</v>
       </c>
       <c r="G86">
         <v>0.262</v>
@@ -8327,28 +8327,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M86">
-        <v>0.9230675999999999</v>
+        <v>0.9340565</v>
       </c>
       <c r="N86">
-        <v>7.4369324</v>
+        <v>7.4259435</v>
       </c>
       <c r="O86">
-        <v>2.60292634</v>
+        <v>2.599080225</v>
       </c>
       <c r="P86">
-        <v>4.83400606</v>
+        <v>4.826863275</v>
       </c>
       <c r="Q86">
-        <v>6.474006060000001</v>
+        <v>6.466863275000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6997737784019801</v>
+        <v>0.739913812014944</v>
       </c>
       <c r="T86">
-        <v>3.213216572631958</v>
+        <v>3.410439497297754</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>9.056758139923881</v>
+        <v>8.950208044160069</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1405458218022416</v>
+        <v>0.1399168390601664</v>
       </c>
       <c r="C87">
-        <v>16.480755019412</v>
+        <v>16.50042342279842</v>
       </c>
       <c r="D87">
-        <v>33.677755019412</v>
+        <v>33.90282342279842</v>
       </c>
       <c r="E87">
-        <v>5.359</v>
+        <v>5.564400000000001</v>
       </c>
       <c r="F87">
-        <v>17.459</v>
+        <v>17.6644</v>
       </c>
       <c r="G87">
         <v>0.262</v>
@@ -8409,28 +8409,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M87">
-        <v>0.9340565</v>
+        <v>0.9450454</v>
       </c>
       <c r="N87">
-        <v>7.4259435</v>
+        <v>7.4149546</v>
       </c>
       <c r="O87">
-        <v>2.599080225</v>
+        <v>2.59523411</v>
       </c>
       <c r="P87">
-        <v>4.826863275</v>
+        <v>4.81972049</v>
       </c>
       <c r="Q87">
-        <v>6.466863275000001</v>
+        <v>6.45972049</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.739913812014944</v>
+        <v>0.7857881361440455</v>
       </c>
       <c r="T87">
-        <v>3.410439497297754</v>
+        <v>3.635837125487234</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.950208044160069</v>
+        <v>8.846135857600068</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1399168390601664</v>
+        <v>0.1392878563180912</v>
       </c>
       <c r="C88">
-        <v>16.50042342279842</v>
+        <v>16.52312032950263</v>
       </c>
       <c r="D88">
-        <v>33.90282342279842</v>
+        <v>34.13092032950263</v>
       </c>
       <c r="E88">
-        <v>5.564400000000001</v>
+        <v>5.769799999999998</v>
       </c>
       <c r="F88">
-        <v>17.6644</v>
+        <v>17.8698</v>
       </c>
       <c r="G88">
         <v>0.262</v>
@@ -8491,28 +8491,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M88">
-        <v>0.9450454</v>
+        <v>0.9560342999999999</v>
       </c>
       <c r="N88">
-        <v>7.4149546</v>
+        <v>7.4039657</v>
       </c>
       <c r="O88">
-        <v>2.59523411</v>
+        <v>2.591387995</v>
       </c>
       <c r="P88">
-        <v>4.81972049</v>
+        <v>4.812577705</v>
       </c>
       <c r="Q88">
-        <v>6.45972049</v>
+        <v>6.452577705</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7857881361440455</v>
+        <v>0.8387200486007012</v>
       </c>
       <c r="T88">
-        <v>3.635837125487234</v>
+        <v>3.895911311859712</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.846135857600068</v>
+        <v>8.744456135098918</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1392878563180912</v>
+        <v>0.1386588735760159</v>
       </c>
       <c r="C89">
-        <v>16.52312032950263</v>
+        <v>16.54890728053568</v>
       </c>
       <c r="D89">
-        <v>34.13092032950263</v>
+        <v>34.36210728053567</v>
       </c>
       <c r="E89">
-        <v>5.769799999999998</v>
+        <v>5.975199999999999</v>
       </c>
       <c r="F89">
-        <v>17.8698</v>
+        <v>18.0752</v>
       </c>
       <c r="G89">
         <v>0.262</v>
@@ -8573,28 +8573,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M89">
-        <v>0.9560342999999999</v>
+        <v>0.9670232</v>
       </c>
       <c r="N89">
-        <v>7.4039657</v>
+        <v>7.3929768</v>
       </c>
       <c r="O89">
-        <v>2.591387995</v>
+        <v>2.58754188</v>
       </c>
       <c r="P89">
-        <v>4.812577705</v>
+        <v>4.80543492</v>
       </c>
       <c r="Q89">
-        <v>6.452577705</v>
+        <v>6.44543492</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8387200486007012</v>
+        <v>0.9004739464667995</v>
       </c>
       <c r="T89">
-        <v>3.895911311859712</v>
+        <v>4.199331195960936</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>8.744456135098918</v>
+        <v>8.645087315381886</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1386588735760159</v>
+        <v>0.1380298908339407</v>
       </c>
       <c r="C90">
-        <v>16.54890728053568</v>
+        <v>16.57784749568034</v>
       </c>
       <c r="D90">
-        <v>34.36210728053567</v>
+        <v>34.59644749568034</v>
       </c>
       <c r="E90">
-        <v>5.975199999999999</v>
+        <v>6.1806</v>
       </c>
       <c r="F90">
-        <v>18.0752</v>
+        <v>18.2806</v>
       </c>
       <c r="G90">
         <v>0.262</v>
@@ -8655,28 +8655,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M90">
-        <v>0.9670232</v>
+        <v>0.9780120999999999</v>
       </c>
       <c r="N90">
-        <v>7.3929768</v>
+        <v>7.381987899999999</v>
       </c>
       <c r="O90">
-        <v>2.58754188</v>
+        <v>2.583695765</v>
       </c>
       <c r="P90">
-        <v>4.80543492</v>
+        <v>4.798292135</v>
       </c>
       <c r="Q90">
-        <v>6.44543492</v>
+        <v>6.438292135</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9004739464667995</v>
+        <v>0.9734558257630973</v>
       </c>
       <c r="T90">
-        <v>4.199331195960936</v>
+        <v>4.557918331716928</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>8.645087315381886</v>
+        <v>8.547951502849504</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1380298908339407</v>
+        <v>0.1374009080918655</v>
       </c>
       <c r="C91">
-        <v>16.57784749568034</v>
+        <v>16.61000593112805</v>
       </c>
       <c r="D91">
-        <v>34.59644749568034</v>
+        <v>34.83400593112805</v>
       </c>
       <c r="E91">
-        <v>6.1806</v>
+        <v>6.386000000000001</v>
       </c>
       <c r="F91">
-        <v>18.2806</v>
+        <v>18.486</v>
       </c>
       <c r="G91">
         <v>0.262</v>
@@ -8737,28 +8737,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M91">
-        <v>0.9780120999999999</v>
+        <v>0.989001</v>
       </c>
       <c r="N91">
-        <v>7.381987899999999</v>
+        <v>7.370998999999999</v>
       </c>
       <c r="O91">
-        <v>2.583695765</v>
+        <v>2.579849649999999</v>
       </c>
       <c r="P91">
-        <v>4.798292135</v>
+        <v>4.79114935</v>
       </c>
       <c r="Q91">
-        <v>6.438292135</v>
+        <v>6.43114935</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9734558257630973</v>
+        <v>1.061034080918655</v>
       </c>
       <c r="T91">
-        <v>4.557918331716928</v>
+        <v>4.988222894624118</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>8.547951502849504</v>
+        <v>8.452974263928954</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1374009080918655</v>
+        <v>0.1367719253497902</v>
       </c>
       <c r="C92">
-        <v>16.61000593112805</v>
+        <v>16.64544933950687</v>
       </c>
       <c r="D92">
-        <v>34.83400593112805</v>
+        <v>35.07484933950687</v>
       </c>
       <c r="E92">
-        <v>6.386000000000001</v>
+        <v>6.591400000000002</v>
       </c>
       <c r="F92">
-        <v>18.486</v>
+        <v>18.6914</v>
       </c>
       <c r="G92">
         <v>0.262</v>
@@ -8819,28 +8819,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M92">
-        <v>0.989001</v>
+        <v>0.9999899000000001</v>
       </c>
       <c r="N92">
-        <v>7.370998999999999</v>
+        <v>7.360010099999999</v>
       </c>
       <c r="O92">
-        <v>2.579849649999999</v>
+        <v>2.576003534999999</v>
       </c>
       <c r="P92">
-        <v>4.79114935</v>
+        <v>4.784006565</v>
       </c>
       <c r="Q92">
-        <v>6.43114935</v>
+        <v>6.424006565000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.061034080918655</v>
+        <v>1.168074170553225</v>
       </c>
       <c r="T92">
-        <v>4.988222894624118</v>
+        <v>5.514150693732907</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>8.452974263928954</v>
+        <v>8.36008443685281</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1367719253497902</v>
+        <v>0.136142942607715</v>
       </c>
       <c r="C93">
-        <v>16.64544933950687</v>
+        <v>16.6842463324168</v>
       </c>
       <c r="D93">
-        <v>35.07484933950687</v>
+        <v>35.3190463324168</v>
       </c>
       <c r="E93">
-        <v>6.591400000000002</v>
+        <v>6.796799999999999</v>
       </c>
       <c r="F93">
-        <v>18.6914</v>
+        <v>18.8968</v>
       </c>
       <c r="G93">
         <v>0.262</v>
@@ -8901,28 +8901,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M93">
-        <v>0.9999899000000001</v>
+        <v>1.0109788</v>
       </c>
       <c r="N93">
-        <v>7.360010099999999</v>
+        <v>7.349021199999999</v>
       </c>
       <c r="O93">
-        <v>2.576003534999999</v>
+        <v>2.572157419999999</v>
       </c>
       <c r="P93">
-        <v>4.784006565</v>
+        <v>4.776863779999999</v>
       </c>
       <c r="Q93">
-        <v>6.424006565000001</v>
+        <v>6.41686378</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.168074170553225</v>
+        <v>1.301874282596439</v>
       </c>
       <c r="T93">
-        <v>5.514150693732907</v>
+        <v>6.171560442618893</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>8.36008443685281</v>
+        <v>8.269213953843543</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.136142942607715</v>
+        <v>0.1355139598656398</v>
       </c>
       <c r="C94">
-        <v>16.6842463324168</v>
+        <v>16.72646744559601</v>
       </c>
       <c r="D94">
-        <v>35.3190463324168</v>
+        <v>35.56666744559601</v>
       </c>
       <c r="E94">
-        <v>6.796799999999999</v>
+        <v>7.0022</v>
       </c>
       <c r="F94">
-        <v>18.8968</v>
+        <v>19.1022</v>
       </c>
       <c r="G94">
         <v>0.262</v>
@@ -8983,28 +8983,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M94">
-        <v>1.0109788</v>
+        <v>1.0219677</v>
       </c>
       <c r="N94">
-        <v>7.349021199999999</v>
+        <v>7.338032299999999</v>
       </c>
       <c r="O94">
-        <v>2.572157419999999</v>
+        <v>2.568311304999999</v>
       </c>
       <c r="P94">
-        <v>4.776863779999999</v>
+        <v>4.769720995</v>
       </c>
       <c r="Q94">
-        <v>6.41686378</v>
+        <v>6.409720995000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.301874282596439</v>
+        <v>1.47390299808057</v>
       </c>
       <c r="T94">
-        <v>6.171560442618893</v>
+        <v>7.016801548329445</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>8.269213953843543</v>
+        <v>8.180297674769955</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1355139598656398</v>
+        <v>0.1348849771235646</v>
       </c>
       <c r="C95">
-        <v>16.72646744559601</v>
+        <v>16.7721852068475</v>
       </c>
       <c r="D95">
-        <v>35.56666744559601</v>
+        <v>35.8177852068475</v>
       </c>
       <c r="E95">
-        <v>7.0022</v>
+        <v>7.207600000000001</v>
       </c>
       <c r="F95">
-        <v>19.1022</v>
+        <v>19.3076</v>
       </c>
       <c r="G95">
         <v>0.262</v>
@@ -9065,28 +9065,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M95">
-        <v>1.0219677</v>
+        <v>1.0329566</v>
       </c>
       <c r="N95">
-        <v>7.338032299999999</v>
+        <v>7.327043399999999</v>
       </c>
       <c r="O95">
-        <v>2.568311304999999</v>
+        <v>2.56446519</v>
       </c>
       <c r="P95">
-        <v>4.769720995</v>
+        <v>4.762578209999999</v>
       </c>
       <c r="Q95">
-        <v>6.409720995000001</v>
+        <v>6.40257821</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.47390299808057</v>
+        <v>1.703274618726078</v>
       </c>
       <c r="T95">
-        <v>7.016801548329445</v>
+        <v>8.143789689276851</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.180297674769955</v>
+        <v>8.093273231421339</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1348849771235646</v>
+        <v>0.1342559943814894</v>
       </c>
       <c r="C96">
-        <v>16.7721852068475</v>
+        <v>16.82147420686374</v>
       </c>
       <c r="D96">
-        <v>35.8177852068475</v>
+        <v>36.07247420686374</v>
       </c>
       <c r="E96">
-        <v>7.207600000000001</v>
+        <v>7.413000000000002</v>
       </c>
       <c r="F96">
-        <v>19.3076</v>
+        <v>19.513</v>
       </c>
       <c r="G96">
         <v>0.262</v>
@@ -9147,28 +9147,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M96">
-        <v>1.0329566</v>
+        <v>1.0439455</v>
       </c>
       <c r="N96">
-        <v>7.327043399999999</v>
+        <v>7.3160545</v>
       </c>
       <c r="O96">
-        <v>2.56446519</v>
+        <v>2.560619075</v>
       </c>
       <c r="P96">
-        <v>4.762578209999999</v>
+        <v>4.755435425</v>
       </c>
       <c r="Q96">
-        <v>6.40257821</v>
+        <v>6.395435425000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.703274618726078</v>
+        <v>2.02439488762979</v>
       </c>
       <c r="T96">
-        <v>8.143789689276851</v>
+        <v>9.72157308660322</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.093273231421339</v>
+        <v>8.008080881616905</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1342559943814894</v>
+        <v>0.1336270116394141</v>
       </c>
       <c r="C97">
-        <v>16.82147420686374</v>
+        <v>16.87441117309485</v>
       </c>
       <c r="D97">
-        <v>36.07247420686374</v>
+        <v>36.33081117309485</v>
       </c>
       <c r="E97">
-        <v>7.413000000000002</v>
+        <v>7.618399999999999</v>
       </c>
       <c r="F97">
-        <v>19.513</v>
+        <v>19.7184</v>
       </c>
       <c r="G97">
         <v>0.262</v>
@@ -9229,28 +9229,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M97">
-        <v>1.0439455</v>
+        <v>1.0549344</v>
       </c>
       <c r="N97">
-        <v>7.3160545</v>
+        <v>7.3050656</v>
       </c>
       <c r="O97">
-        <v>2.560619075</v>
+        <v>2.55677296</v>
       </c>
       <c r="P97">
-        <v>4.755435425</v>
+        <v>4.74829264</v>
       </c>
       <c r="Q97">
-        <v>6.395435425000001</v>
+        <v>6.38829264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.02439488762979</v>
+        <v>2.506075290985358</v>
       </c>
       <c r="T97">
-        <v>9.72157308660322</v>
+        <v>12.08824818259277</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.008080881616905</v>
+        <v>7.924663372433396</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1336270116394141</v>
+        <v>0.1329980288973389</v>
       </c>
       <c r="C98">
-        <v>16.87441117309485</v>
+        <v>16.93107504681353</v>
       </c>
       <c r="D98">
-        <v>36.33081117309485</v>
+        <v>36.59287504681353</v>
       </c>
       <c r="E98">
-        <v>7.618399999999999</v>
+        <v>7.8238</v>
       </c>
       <c r="F98">
-        <v>19.7184</v>
+        <v>19.9238</v>
       </c>
       <c r="G98">
         <v>0.262</v>
@@ -9311,28 +9311,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M98">
-        <v>1.0549344</v>
+        <v>1.0659233</v>
       </c>
       <c r="N98">
-        <v>7.3050656</v>
+        <v>7.2940767</v>
       </c>
       <c r="O98">
-        <v>2.55677296</v>
+        <v>2.552926845</v>
       </c>
       <c r="P98">
-        <v>4.74829264</v>
+        <v>4.741149855</v>
       </c>
       <c r="Q98">
-        <v>6.38829264</v>
+        <v>6.381149855</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.506075290985351</v>
+        <v>3.308875963244628</v>
       </c>
       <c r="T98">
-        <v>12.08824818259274</v>
+        <v>16.03270667590865</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.924663372433396</v>
+        <v>7.842965811892845</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1329980288973389</v>
+        <v>0.1323690461552637</v>
       </c>
       <c r="C99">
-        <v>16.93107504681353</v>
+        <v>16.99154706353971</v>
       </c>
       <c r="D99">
-        <v>36.59287504681353</v>
+        <v>36.8587470635397</v>
       </c>
       <c r="E99">
-        <v>7.8238</v>
+        <v>8.029199999999998</v>
       </c>
       <c r="F99">
-        <v>19.9238</v>
+        <v>20.1292</v>
       </c>
       <c r="G99">
         <v>0.262</v>
@@ -9393,28 +9393,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M99">
-        <v>1.0659233</v>
+        <v>1.0769122</v>
       </c>
       <c r="N99">
-        <v>7.2940767</v>
+        <v>7.2830878</v>
       </c>
       <c r="O99">
-        <v>2.552926845</v>
+        <v>2.54908073</v>
       </c>
       <c r="P99">
-        <v>4.741149855</v>
+        <v>4.734007070000001</v>
       </c>
       <c r="Q99">
-        <v>6.381149855</v>
+        <v>6.374007070000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.308875963244628</v>
+        <v>4.91447730776318</v>
       </c>
       <c r="T99">
-        <v>16.03270667590865</v>
+        <v>23.92162366254045</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.842965811892845</v>
+        <v>7.762935548506184</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1323690461552637</v>
+        <v>0.1317400634131885</v>
       </c>
       <c r="C100">
-        <v>16.99154706353971</v>
+        <v>17.05591083699678</v>
       </c>
       <c r="D100">
-        <v>36.8587470635397</v>
+        <v>37.12851083699677</v>
       </c>
       <c r="E100">
-        <v>8.029199999999998</v>
+        <v>8.234599999999999</v>
       </c>
       <c r="F100">
-        <v>20.1292</v>
+        <v>20.3346</v>
       </c>
       <c r="G100">
         <v>0.262</v>
@@ -9475,28 +9475,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="M100">
-        <v>1.0769122</v>
+        <v>1.0879011</v>
       </c>
       <c r="N100">
-        <v>7.2830878</v>
+        <v>7.2720989</v>
       </c>
       <c r="O100">
-        <v>2.54908073</v>
+        <v>2.545234615</v>
       </c>
       <c r="P100">
-        <v>4.734007070000001</v>
+        <v>4.726864285</v>
       </c>
       <c r="Q100">
-        <v>6.374007070000001</v>
+        <v>6.366864285</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.91447730776318</v>
+        <v>9.731281341318839</v>
       </c>
       <c r="T100">
-        <v>23.92162366254045</v>
+        <v>47.58837462243589</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>7.762935548506184</v>
+        <v>7.684522058117232</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1317400634131885</v>
-      </c>
-      <c r="C101">
-        <v>17.05591083699678</v>
-      </c>
-      <c r="D101">
-        <v>37.12851083699677</v>
-      </c>
-      <c r="E101">
-        <v>8.234599999999999</v>
-      </c>
-      <c r="F101">
-        <v>20.3346</v>
-      </c>
-      <c r="G101">
-        <v>0.262</v>
-      </c>
-      <c r="H101">
-        <v>8.44</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10</v>
-      </c>
-      <c r="K101">
-        <v>1.640000000000001</v>
-      </c>
-      <c r="L101">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="M101">
-        <v>1.0879011</v>
-      </c>
-      <c r="N101">
-        <v>7.2720989</v>
-      </c>
-      <c r="O101">
-        <v>2.545234615</v>
-      </c>
-      <c r="P101">
-        <v>4.726864285</v>
-      </c>
-      <c r="Q101">
-        <v>6.366864285</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.731281341318839</v>
-      </c>
-      <c r="T101">
-        <v>47.58837462243589</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.034775</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>7.684522058117232</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
